--- a/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
+++ b/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2002FC36-5E3A-4883-8D8A-124FFE4A23A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A20821-9A7B-4D69-8EB5-6322CD6D2AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="1905" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -10779,10 +10779,12 @@
         <v>380</v>
       </c>
       <c r="G37" s="35">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H37" s="32">
-        <v>9.8483224013816553E-2</v>
+        <f>TAN(ACOS(0.95))*G37</f>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -10805,10 +10807,12 @@
         <v>380</v>
       </c>
       <c r="G38" s="35">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H38" s="32">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" ref="H38:H46" si="0">TAN(ACOS(0.95))*G38</f>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -10831,10 +10835,12 @@
         <v>380</v>
       </c>
       <c r="G39" s="35">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H39" s="32">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -10857,10 +10863,12 @@
         <v>380</v>
       </c>
       <c r="G40" s="35">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H40" s="32">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -10883,10 +10891,12 @@
         <v>380</v>
       </c>
       <c r="G41" s="35">
-        <v>0.26103399999999999</v>
+        <f>0.261034-0.05+0.18</f>
+        <v>0.39103399999999999</v>
       </c>
       <c r="H41" s="32">
-        <v>8.5797726711259376E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.1285266603845116</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -10909,10 +10919,12 @@
         <v>380</v>
       </c>
       <c r="G42" s="35">
-        <v>0.211034</v>
+        <f>0.211034+0.18</f>
+        <v>0.39103399999999999</v>
       </c>
       <c r="H42" s="32">
-        <v>6.9363521452316224E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.1285266603845116</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -10935,10 +10947,12 @@
         <v>380</v>
       </c>
       <c r="G43" s="32">
-        <v>0.05</v>
+        <f>1.79</f>
+        <v>1.79</v>
       </c>
       <c r="H43" s="32">
-        <v>1.6434205258943162E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.58834454827016514</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -10961,10 +10975,12 @@
         <v>380</v>
       </c>
       <c r="G44" s="35">
-        <v>0.10199</v>
+        <f>0.10199-0.05+0.12</f>
+        <v>0.17198999999999998</v>
       </c>
       <c r="H44" s="32">
-        <v>3.3522491887192259E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.6530379249712673E-2</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -10987,10 +11003,12 @@
         <v>380</v>
       </c>
       <c r="G45" s="32">
-        <v>0.05</v>
+        <f>0.05-0.05+2.05</f>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H45" s="32">
-        <v>1.6434205258943162E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.67380241561666954</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -11013,10 +11031,12 @@
         <v>380</v>
       </c>
       <c r="G46" s="35">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H46" s="32">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -11110,7 +11130,7 @@
         <v>263</v>
       </c>
       <c r="E2">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -11119,19 +11139,18 @@
         <v>38</v>
       </c>
       <c r="I2" s="32">
-        <f>0.1/2</f>
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
         <f>E2/2000</f>
-        <v>0.98599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-0.98599999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -11159,7 +11178,7 @@
         <v>264</v>
       </c>
       <c r="E3">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="F3">
         <v>380</v>
@@ -11168,26 +11187,25 @@
         <v>39</v>
       </c>
       <c r="I3" s="32">
-        <f t="shared" ref="I3:I7" si="0">0.1/2</f>
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K66" si="1">E3/2000</f>
-        <v>0.98599999999999999</v>
+        <f t="shared" ref="K3:K66" si="0">E3/2000</f>
+        <v>1.17</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L10" si="2">-K3</f>
-        <v>-0.98599999999999999</v>
+        <f t="shared" ref="L3:L10" si="1">-K3</f>
+        <v>-1.17</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M10" si="3">5/2</f>
+        <f t="shared" ref="M3:M10" si="2">5/2</f>
         <v>2.5</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N10" si="4">-M3</f>
+        <f t="shared" ref="N3:N10" si="3">-M3</f>
         <v>-2.5</v>
       </c>
       <c r="O3">
@@ -11208,7 +11226,7 @@
         <v>265</v>
       </c>
       <c r="E4">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="F4">
         <v>380</v>
@@ -11217,26 +11235,25 @@
         <v>41</v>
       </c>
       <c r="I4" s="32">
+        <v>0.24</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+        <v>1.17</v>
+      </c>
+      <c r="L4">
         <f t="shared" si="1"/>
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="L4">
+        <v>-1.17</v>
+      </c>
+      <c r="M4">
         <f t="shared" si="2"/>
-        <v>-0.49299999999999999</v>
-      </c>
-      <c r="M4">
+        <v>2.5</v>
+      </c>
+      <c r="N4">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O4">
@@ -11257,7 +11274,7 @@
         <v>266</v>
       </c>
       <c r="E5">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="F5">
         <v>380</v>
@@ -11266,26 +11283,25 @@
         <v>42</v>
       </c>
       <c r="I5" s="32">
+        <v>0.24</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+        <v>1.17</v>
+      </c>
+      <c r="L5">
         <f t="shared" si="1"/>
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="L5">
+        <v>-1.17</v>
+      </c>
+      <c r="M5">
         <f t="shared" si="2"/>
-        <v>-0.49299999999999999</v>
-      </c>
-      <c r="M5">
+        <v>2.5</v>
+      </c>
+      <c r="N5">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O5">
@@ -11306,7 +11322,7 @@
         <v>267</v>
       </c>
       <c r="E6">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="F6">
         <v>380</v>
@@ -11315,26 +11331,25 @@
         <v>43</v>
       </c>
       <c r="I6" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+        <v>0.6</v>
+      </c>
+      <c r="L6">
         <f t="shared" si="1"/>
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="L6">
+        <v>-0.6</v>
+      </c>
+      <c r="M6">
         <f t="shared" si="2"/>
-        <v>-0.56399999999999995</v>
-      </c>
-      <c r="M6">
+        <v>2.5</v>
+      </c>
+      <c r="N6">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O6">
@@ -11355,7 +11370,7 @@
         <v>268</v>
       </c>
       <c r="E7">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="F7">
         <v>380</v>
@@ -11364,26 +11379,25 @@
         <v>44</v>
       </c>
       <c r="I7" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+        <v>0.6</v>
+      </c>
+      <c r="L7">
         <f t="shared" si="1"/>
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="L7">
+        <v>-0.6</v>
+      </c>
+      <c r="M7">
         <f t="shared" si="2"/>
-        <v>-0.56399999999999995</v>
-      </c>
-      <c r="M7">
+        <v>2.5</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O7">
@@ -11404,7 +11418,7 @@
         <v>269</v>
       </c>
       <c r="E8">
-        <v>1000</v>
+        <v>10800</v>
       </c>
       <c r="F8">
         <v>380</v>
@@ -11413,26 +11427,26 @@
         <v>35</v>
       </c>
       <c r="I8" s="35">
-        <f>0.100864/2</f>
-        <v>5.0431999999999998E-2</v>
+        <f>0.100864/2 - 0.05 + 1.79</f>
+        <v>1.790432</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
+        <f t="shared" si="0"/>
+        <v>5.4</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="L8">
+        <v>-5.4</v>
+      </c>
+      <c r="M8">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
-      </c>
-      <c r="M8">
+        <v>2.5</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O8">
@@ -11453,7 +11467,7 @@
         <v>270</v>
       </c>
       <c r="E9">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="F9">
         <v>380</v>
@@ -11462,26 +11476,26 @@
         <v>36</v>
       </c>
       <c r="I9" s="32">
-        <f>0.1/2</f>
-        <v>0.05</v>
+        <f>0.12</f>
+        <v>0.12</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="L9">
+        <v>-0.6</v>
+      </c>
+      <c r="M9">
         <f t="shared" si="2"/>
-        <v>-0.35</v>
-      </c>
-      <c r="M9">
+        <v>2.5</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O9">
@@ -11502,7 +11516,7 @@
         <v>271</v>
       </c>
       <c r="E10" s="10">
-        <v>700</v>
+        <v>11100</v>
       </c>
       <c r="F10" s="10">
         <v>380</v>
@@ -11512,26 +11526,26 @@
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="35">
-        <f>0.49222/2</f>
-        <v>0.24611</v>
+        <f>0.49222/2 - 0.05 + 2.05</f>
+        <v>2.2461099999999998</v>
       </c>
       <c r="J10" s="10">
         <v>0</v>
       </c>
       <c r="K10">
+        <f t="shared" si="0"/>
+        <v>5.55</v>
+      </c>
+      <c r="L10" s="10">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="L10" s="10">
+        <v>-5.55</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="2"/>
-        <v>-0.35</v>
-      </c>
-      <c r="M10">
+        <v>2.5</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O10" s="10">
@@ -11572,7 +11586,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
       <c r="L11">
@@ -11613,25 +11627,25 @@
         <v>28</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I14" si="5">0.6*E12/2000</f>
+        <f t="shared" ref="I12:I14" si="4">0.6*E12/2000</f>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" ref="M12:M75" si="6">0.33*E12/2000</f>
+        <f t="shared" ref="M12:M75" si="5">0.33*E12/2000</f>
         <v>2.0625000000000001E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:N13" si="7">-M12</f>
+        <f t="shared" ref="N12:N13" si="6">-M12</f>
         <v>-2.0625000000000001E-2</v>
       </c>
       <c r="O12">
@@ -11661,25 +11675,25 @@
         <v>29</v>
       </c>
       <c r="I13">
+        <f t="shared" si="4"/>
+        <v>2.1000000000000003E-3</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <f t="shared" si="5"/>
-        <v>2.1000000000000003E-3</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
+        <v>1.155E-3</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="6"/>
-        <v>1.155E-3</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="7"/>
         <v>-1.155E-3</v>
       </c>
       <c r="O13">
@@ -11709,25 +11723,25 @@
         <v>12</v>
       </c>
       <c r="I14">
+        <f t="shared" si="4"/>
+        <v>1.14E-2</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1.9E-2</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="5"/>
-        <v>1.14E-2</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
-        <v>1.9E-2</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="6"/>
         <v>6.2700000000000004E-3</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:N77" si="8">-M14</f>
+        <f t="shared" ref="N14:N77" si="7">-M14</f>
         <v>-6.2700000000000004E-3</v>
       </c>
       <c r="O14">
@@ -11764,18 +11778,18 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.24249999999999999</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.0024999999999999E-2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-8.0024999999999999E-2</v>
       </c>
       <c r="O15">
@@ -11812,18 +11826,18 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.4E-2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.92E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.92E-3</v>
       </c>
       <c r="O16" s="5">
@@ -11859,25 +11873,25 @@
         <v>11</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I80" si="9">0.6*E17/2000</f>
+        <f t="shared" ref="I17:I80" si="8">0.6*E17/2000</f>
         <v>0.13650000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.22750000000000001</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.5075000000000003E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.5075000000000003E-2</v>
       </c>
       <c r="O17">
@@ -11907,25 +11921,25 @@
         <v>28</v>
       </c>
       <c r="I18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.25319999999999998</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.42199999999999999</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.13926000000000002</v>
       </c>
       <c r="N18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.13926000000000002</v>
       </c>
       <c r="O18">
@@ -11955,25 +11969,25 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.1599999999999998E-2</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.188E-2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O19" s="5">
@@ -12009,25 +12023,25 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.1599999999999998E-2</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.188E-2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O20" s="5">
@@ -12063,25 +12077,25 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.9299999999999995E-2</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.5500000000000003E-2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.1615000000000002E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.1615000000000002E-2</v>
       </c>
       <c r="O21" s="5">
@@ -12117,25 +12131,25 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1077</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9234999999999996E-2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O22" s="5">
@@ -12171,25 +12185,25 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1077</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9234999999999996E-2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O23" s="5">
@@ -12225,25 +12239,25 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10829999999999999</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.18049999999999999</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9565000000000007E-2</v>
       </c>
       <c r="N24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9565000000000007E-2</v>
       </c>
       <c r="O24" s="5">
@@ -12279,25 +12293,25 @@
         <v>18</v>
       </c>
       <c r="I25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1077</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9234999999999996E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O25">
@@ -12327,25 +12341,25 @@
         <v>18</v>
       </c>
       <c r="I26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.108</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9400000000000008E-2</v>
       </c>
       <c r="N26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9400000000000008E-2</v>
       </c>
       <c r="O26">
@@ -12375,25 +12389,25 @@
         <v>25</v>
       </c>
       <c r="I27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1278</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.0290000000000005E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O27">
@@ -12423,25 +12437,25 @@
         <v>25</v>
       </c>
       <c r="I28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1245</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.20749999999999999</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.8475000000000008E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O28">
@@ -12471,25 +12485,25 @@
         <v>13</v>
       </c>
       <c r="I29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.1500000000000002E-2</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.3695000000000001E-2</v>
       </c>
       <c r="N29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.3695000000000001E-2</v>
       </c>
       <c r="O29">
@@ -12519,25 +12533,25 @@
         <v>33</v>
       </c>
       <c r="I30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.3600000000000005E-2</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.848E-2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.848E-2</v>
       </c>
       <c r="O30">
@@ -12567,25 +12581,25 @@
         <v>24</v>
       </c>
       <c r="I31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.1999999999999989E-3</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.96E-3</v>
       </c>
       <c r="N31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O31">
@@ -12615,25 +12629,25 @@
         <v>24</v>
       </c>
       <c r="I32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.1999999999999989E-3</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.96E-3</v>
       </c>
       <c r="N32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O32">
@@ -12663,25 +12677,25 @@
         <v>24</v>
       </c>
       <c r="I33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.11</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.6300000000000006E-2</v>
       </c>
       <c r="N33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.6300000000000006E-2</v>
       </c>
       <c r="O33">
@@ -12711,25 +12725,25 @@
         <v>28</v>
       </c>
       <c r="I34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.3699999999999999E-2</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.95E-2</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.3035E-2</v>
       </c>
       <c r="N34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.3035E-2</v>
       </c>
       <c r="O34">
@@ -12759,25 +12773,25 @@
         <v>11</v>
       </c>
       <c r="I35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1305</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2175</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1775000000000005E-2</v>
       </c>
       <c r="N35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O35">
@@ -12807,25 +12821,25 @@
         <v>11</v>
       </c>
       <c r="I36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1305</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2175</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1775000000000005E-2</v>
       </c>
       <c r="N36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O36">
@@ -12855,25 +12869,25 @@
         <v>22</v>
       </c>
       <c r="I37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.18</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="N37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O37">
@@ -12903,25 +12917,25 @@
         <v>23</v>
       </c>
       <c r="I38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O38">
@@ -12951,25 +12965,25 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.9700000000000004E-2</v>
       </c>
       <c r="N39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.9700000000000004E-2</v>
       </c>
       <c r="O39" s="5">
@@ -13005,25 +13019,25 @@
         <v>26</v>
       </c>
       <c r="I40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.192</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.32</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.10560000000000001</v>
       </c>
       <c r="N40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.10560000000000001</v>
       </c>
       <c r="O40">
@@ -13053,25 +13067,25 @@
         <v>26</v>
       </c>
       <c r="I41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.38250000000000001</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.63749999999999996</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.21037500000000001</v>
       </c>
       <c r="N41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.21037500000000001</v>
       </c>
       <c r="O41">
@@ -13101,25 +13115,25 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.105</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.7750000000000003E-2</v>
       </c>
       <c r="N42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.7750000000000003E-2</v>
       </c>
       <c r="O42" s="5">
@@ -13155,25 +13169,25 @@
         <v>9</v>
       </c>
       <c r="I43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.89E-2</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.15E-2</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0395000000000001E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O43" s="5">
@@ -13209,25 +13223,25 @@
         <v>9</v>
       </c>
       <c r="I44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.89E-2</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.15E-2</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0395000000000001E-2</v>
       </c>
       <c r="N44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O44" s="5">
@@ -13263,25 +13277,25 @@
         <v>26</v>
       </c>
       <c r="I45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.115</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7950000000000005E-2</v>
       </c>
       <c r="N45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.7950000000000005E-2</v>
       </c>
       <c r="O45">
@@ -13311,25 +13325,25 @@
         <v>30</v>
       </c>
       <c r="I46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.4450000000000002E-3</v>
       </c>
       <c r="N46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.4450000000000002E-3</v>
       </c>
       <c r="O46">
@@ -13359,25 +13373,25 @@
         <v>16</v>
       </c>
       <c r="I47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.1250000000000002E-3</v>
       </c>
       <c r="N47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-4.1250000000000002E-3</v>
       </c>
       <c r="O47">
@@ -13407,25 +13421,25 @@
         <v>22</v>
       </c>
       <c r="I48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6E-2</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.28E-3</v>
       </c>
       <c r="N48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O48">
@@ -13455,25 +13469,25 @@
         <v>2</v>
       </c>
       <c r="I49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.112E-2</v>
       </c>
       <c r="N49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.112E-2</v>
       </c>
       <c r="O49" s="5">
@@ -13509,25 +13523,25 @@
         <v>15</v>
       </c>
       <c r="I50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.8599999999999998E-2</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.1E-2</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0230000000000001E-2</v>
       </c>
       <c r="N50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O50">
@@ -13557,25 +13571,25 @@
         <v>15</v>
       </c>
       <c r="I51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.75E-2</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.0750000000000015E-3</v>
       </c>
       <c r="N51">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O51">
@@ -13605,25 +13619,25 @@
         <v>15</v>
       </c>
       <c r="I52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.4700000000000003E-2</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.1245</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.1085000000000003E-2</v>
       </c>
       <c r="N52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-4.1085000000000003E-2</v>
       </c>
       <c r="O52">
@@ -13653,25 +13667,25 @@
         <v>12</v>
       </c>
       <c r="I53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>4.3199999999999995E-2</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.376E-2</v>
       </c>
       <c r="N53">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O53">
@@ -13701,25 +13715,25 @@
         <v>10</v>
       </c>
       <c r="I54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.4399999999999994E-2</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.124</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.0920000000000005E-2</v>
       </c>
       <c r="N54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-4.0920000000000005E-2</v>
       </c>
       <c r="O54">
@@ -13749,25 +13763,25 @@
         <v>10</v>
       </c>
       <c r="I55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.0899999999999997E-2</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.1499999999999997E-2</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.6995E-2</v>
       </c>
       <c r="N55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.6995E-2</v>
       </c>
       <c r="O55">
@@ -13797,25 +13811,25 @@
         <v>10</v>
       </c>
       <c r="I56">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.7500000000000004E-2</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.1125</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7124999999999998E-2</v>
       </c>
       <c r="N56">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.7124999999999998E-2</v>
       </c>
       <c r="O56">
@@ -13845,25 +13859,25 @@
         <v>15</v>
       </c>
       <c r="I57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.0099999999999996E-2</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3500000000000002E-2</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.1054999999999999E-2</v>
       </c>
       <c r="N57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.1054999999999999E-2</v>
       </c>
       <c r="O57">
@@ -13893,25 +13907,25 @@
         <v>12</v>
       </c>
       <c r="I58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13800000000000001</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.23</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.5900000000000009E-2</v>
       </c>
       <c r="N58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.5900000000000009E-2</v>
       </c>
       <c r="O58">
@@ -13941,25 +13955,25 @@
         <v>12</v>
       </c>
       <c r="I59">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.114</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.2700000000000006E-2</v>
       </c>
       <c r="N59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-6.2700000000000006E-2</v>
       </c>
       <c r="O59">
@@ -13989,25 +14003,25 @@
         <v>29</v>
       </c>
       <c r="I60">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13200000000000001</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2600000000000012E-2</v>
       </c>
       <c r="N60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2600000000000012E-2</v>
       </c>
       <c r="O60">
@@ -14037,25 +14051,25 @@
         <v>28</v>
       </c>
       <c r="I61">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1278</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.0290000000000005E-2</v>
       </c>
       <c r="N61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O61">
@@ -14085,25 +14099,25 @@
         <v>22</v>
       </c>
       <c r="I62">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10529999999999999</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17549999999999999</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.7915000000000008E-2</v>
       </c>
       <c r="N62">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.7915000000000008E-2</v>
       </c>
       <c r="O62">
@@ -14133,25 +14147,25 @@
         <v>22</v>
       </c>
       <c r="I63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1245</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.20749999999999999</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.8475000000000008E-2</v>
       </c>
       <c r="N63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O63">
@@ -14181,25 +14195,25 @@
         <v>30</v>
       </c>
       <c r="I64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.1999999999999989E-3</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.96E-3</v>
       </c>
       <c r="N64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O64">
@@ -14229,25 +14243,25 @@
         <v>21</v>
       </c>
       <c r="I65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13109999999999999</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2185</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2105000000000002E-2</v>
       </c>
       <c r="N65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O65">
@@ -14277,25 +14291,25 @@
         <v>21</v>
       </c>
       <c r="I66">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13109999999999999</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2185</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2105000000000002E-2</v>
       </c>
       <c r="N66">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O66">
@@ -14325,25 +14339,25 @@
         <v>21</v>
       </c>
       <c r="I67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13109999999999999</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67">
-        <f t="shared" ref="K67:K130" si="10">E67/2000</f>
+        <f t="shared" ref="K67:K130" si="9">E67/2000</f>
         <v>0.2185</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2105000000000002E-2</v>
       </c>
       <c r="N67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O67">
@@ -14373,25 +14387,25 @@
         <v>15</v>
       </c>
       <c r="I68">
+        <f t="shared" si="8"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
         <f t="shared" si="9"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="10"/>
         <v>0.2175</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
       <c r="M68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1775000000000005E-2</v>
       </c>
       <c r="N68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O68">
@@ -14421,25 +14435,25 @@
         <v>22</v>
       </c>
       <c r="I69">
+        <f t="shared" si="8"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
         <f t="shared" si="9"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <f t="shared" si="10"/>
         <v>0.06</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="N69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O69">
@@ -14469,25 +14483,25 @@
         <v>22</v>
       </c>
       <c r="I70">
+        <f t="shared" si="8"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
         <f t="shared" si="9"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <f t="shared" si="10"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.94E-3</v>
       </c>
       <c r="N70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O70">
@@ -14517,25 +14531,25 @@
         <v>23</v>
       </c>
       <c r="I71">
+        <f t="shared" si="8"/>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
         <f t="shared" si="9"/>
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <f t="shared" si="10"/>
         <v>1.15E-2</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7950000000000002E-3</v>
       </c>
       <c r="N71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.7950000000000002E-3</v>
       </c>
       <c r="O71">
@@ -14565,25 +14579,25 @@
         <v>8</v>
       </c>
       <c r="I72">
+        <f t="shared" si="8"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
         <f t="shared" si="9"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <f t="shared" si="10"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
       <c r="M72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O72" s="5">
@@ -14619,25 +14633,25 @@
         <v>51</v>
       </c>
       <c r="I73">
+        <f t="shared" si="8"/>
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
         <f t="shared" si="9"/>
-        <v>3.6600000000000001E-2</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <f t="shared" si="10"/>
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.0130000000000002E-2</v>
       </c>
       <c r="N73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O73">
@@ -14667,25 +14681,25 @@
         <v>17</v>
       </c>
       <c r="I74">
+        <f t="shared" si="8"/>
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
         <f t="shared" si="9"/>
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <f t="shared" si="10"/>
         <v>1.55E-2</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
       <c r="M74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.1150000000000006E-3</v>
       </c>
       <c r="N74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.1150000000000006E-3</v>
       </c>
       <c r="O74">
@@ -14715,25 +14729,25 @@
         <v>23</v>
       </c>
       <c r="I75">
+        <f t="shared" si="8"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
         <f t="shared" si="9"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <f t="shared" si="10"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
       <c r="M75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O75">
@@ -14763,25 +14777,25 @@
         <v>8</v>
       </c>
       <c r="I76">
+        <f t="shared" si="8"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
         <f t="shared" si="9"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <f t="shared" si="10"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="M76">
-        <f t="shared" ref="M76:M139" si="11">0.33*E76/2000</f>
+        <f t="shared" ref="M76:M139" si="10">0.33*E76/2000</f>
         <v>5.94E-3</v>
       </c>
       <c r="N76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O76" s="5">
@@ -14817,25 +14831,25 @@
         <v>12</v>
       </c>
       <c r="I77">
+        <f t="shared" si="8"/>
+        <v>1.95E-2</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
         <f t="shared" si="9"/>
-        <v>1.95E-2</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
         <f t="shared" si="10"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <f t="shared" si="11"/>
         <v>1.0725E-2</v>
       </c>
       <c r="N77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O77">
@@ -14865,25 +14879,25 @@
         <v>14</v>
       </c>
       <c r="I78">
+        <f t="shared" si="8"/>
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
         <f t="shared" si="9"/>
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78">
+        <v>1.6E-2</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
         <f t="shared" si="10"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <f t="shared" si="11"/>
         <v>5.28E-3</v>
       </c>
       <c r="N78">
-        <f t="shared" ref="N78:N139" si="12">-M78</f>
+        <f t="shared" ref="N78:N139" si="11">-M78</f>
         <v>-5.28E-3</v>
       </c>
       <c r="O78">
@@ -14913,25 +14927,25 @@
         <v>29</v>
       </c>
       <c r="I79">
+        <f t="shared" si="8"/>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
         <f t="shared" si="9"/>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
         <f t="shared" si="10"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
+        <v>2.4750000000000001E-2</v>
+      </c>
+      <c r="N79">
         <f t="shared" si="11"/>
-        <v>2.4750000000000001E-2</v>
-      </c>
-      <c r="N79">
-        <f t="shared" si="12"/>
         <v>-2.4750000000000001E-2</v>
       </c>
       <c r="O79">
@@ -14961,25 +14975,25 @@
         <v>51</v>
       </c>
       <c r="I80">
+        <f t="shared" si="8"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
         <f t="shared" si="9"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
+        <v>0.03</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
         <f t="shared" si="10"/>
-        <v>0.03</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="N80">
         <f t="shared" si="11"/>
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="N80">
-        <f t="shared" si="12"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O80">
@@ -15009,25 +15023,25 @@
         <v>50</v>
       </c>
       <c r="I81">
-        <f t="shared" ref="I81:I82" si="13">0.6*E81/2000</f>
+        <f t="shared" ref="I81:I82" si="12">0.6*E81/2000</f>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
+        <f t="shared" si="9"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
         <f t="shared" si="10"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
+        <v>5.28E-3</v>
+      </c>
+      <c r="N81">
         <f t="shared" si="11"/>
-        <v>5.28E-3</v>
-      </c>
-      <c r="N81">
-        <f t="shared" si="12"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O81">
@@ -15058,25 +15072,25 @@
       </c>
       <c r="H82" s="10"/>
       <c r="I82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82">
+        <f t="shared" si="9"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L82" s="10">
+        <v>0</v>
+      </c>
+      <c r="M82">
         <f t="shared" si="10"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L82" s="10">
-        <v>0</v>
-      </c>
-      <c r="M82">
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N82">
         <f t="shared" si="11"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N82">
-        <f t="shared" si="12"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O82" s="10">
@@ -15117,18 +15131,18 @@
         <v>0</v>
       </c>
       <c r="K83">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
         <f t="shared" si="10"/>
-        <v>0.3</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="N83">
         <f t="shared" si="11"/>
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="N83">
-        <f t="shared" si="12"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O83">
@@ -15158,25 +15172,25 @@
         <v>13</v>
       </c>
       <c r="I84" s="28">
-        <f t="shared" ref="I84:I109" si="14">0.35*K84</f>
+        <f t="shared" ref="I84:I109" si="13">0.35*K84</f>
         <v>2.2574999999999998E-2</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
+        <f t="shared" si="9"/>
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
         <f t="shared" si="10"/>
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
+        <v>2.1285000000000002E-2</v>
+      </c>
+      <c r="N84">
         <f t="shared" si="11"/>
-        <v>2.1285000000000002E-2</v>
-      </c>
-      <c r="N84">
-        <f t="shared" si="12"/>
         <v>-2.1285000000000002E-2</v>
       </c>
       <c r="O84">
@@ -15206,25 +15220,25 @@
         <v>12</v>
       </c>
       <c r="I85" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.0999999999999998E-2</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
+        <f t="shared" si="9"/>
+        <v>0.06</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
         <f t="shared" si="10"/>
-        <v>0.06</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="N85">
         <f t="shared" si="11"/>
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="N85">
-        <f t="shared" si="12"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O85">
@@ -15254,25 +15268,25 @@
         <v>12</v>
       </c>
       <c r="I86" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.89E-2</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
+        <f t="shared" si="9"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
         <f t="shared" si="10"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
+        <v>1.7819999999999999E-2</v>
+      </c>
+      <c r="N86">
         <f t="shared" si="11"/>
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="N86">
-        <f t="shared" si="12"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O86">
@@ -15302,25 +15316,25 @@
         <v>15</v>
       </c>
       <c r="I87" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.1349999999999997E-2</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
+        <f t="shared" si="9"/>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
         <f t="shared" si="10"/>
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
+        <v>2.0130000000000002E-2</v>
+      </c>
+      <c r="N87">
         <f t="shared" si="11"/>
-        <v>2.0130000000000002E-2</v>
-      </c>
-      <c r="N87">
-        <f t="shared" si="12"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O87">
@@ -15350,25 +15364,25 @@
         <v>6</v>
       </c>
       <c r="I88" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.9925E-2</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
+        <f t="shared" si="9"/>
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
         <f t="shared" si="10"/>
-        <v>8.5500000000000007E-2</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
+        <v>2.8215E-2</v>
+      </c>
+      <c r="N88">
         <f t="shared" si="11"/>
-        <v>2.8215E-2</v>
-      </c>
-      <c r="N88">
-        <f t="shared" si="12"/>
         <v>-2.8215E-2</v>
       </c>
       <c r="O88" s="5">
@@ -15404,25 +15418,25 @@
         <v>5</v>
       </c>
       <c r="I89" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.5199999999999997E-2</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
         <f t="shared" si="10"/>
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
+        <v>2.376E-2</v>
+      </c>
+      <c r="N89">
         <f t="shared" si="11"/>
-        <v>2.376E-2</v>
-      </c>
-      <c r="N89">
-        <f t="shared" si="12"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O89" s="5">
@@ -15458,25 +15472,25 @@
         <v>5</v>
       </c>
       <c r="I90" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4.9874999999999996E-2</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
+        <f t="shared" si="9"/>
+        <v>0.14249999999999999</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
         <f t="shared" si="10"/>
-        <v>0.14249999999999999</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
+        <v>4.7025000000000004E-2</v>
+      </c>
+      <c r="N90">
         <f t="shared" si="11"/>
-        <v>4.7025000000000004E-2</v>
-      </c>
-      <c r="N90">
-        <f t="shared" si="12"/>
         <v>-4.7025000000000004E-2</v>
       </c>
       <c r="O90" s="5">
@@ -15512,25 +15526,25 @@
         <v>28</v>
       </c>
       <c r="I91" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.7849999999999998E-2</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
+        <f t="shared" si="9"/>
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
         <f t="shared" si="10"/>
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
+        <v>1.6830000000000001E-2</v>
+      </c>
+      <c r="N91">
         <f t="shared" si="11"/>
-        <v>1.6830000000000001E-2</v>
-      </c>
-      <c r="N91">
-        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O91">
@@ -15560,25 +15574,25 @@
         <v>30</v>
       </c>
       <c r="I92" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.4437499999999999E-2</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
+        <f t="shared" si="9"/>
+        <v>4.1250000000000002E-2</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
         <f t="shared" si="10"/>
-        <v>4.1250000000000002E-2</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
+        <v>1.3612500000000001E-2</v>
+      </c>
+      <c r="N92">
         <f t="shared" si="11"/>
-        <v>1.3612500000000001E-2</v>
-      </c>
-      <c r="N92">
-        <f t="shared" si="12"/>
         <v>-1.3612500000000001E-2</v>
       </c>
       <c r="O92">
@@ -15608,25 +15622,25 @@
         <v>8</v>
       </c>
       <c r="I93" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.09725E-2</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
+        <f t="shared" si="9"/>
+        <v>3.1350000000000003E-2</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
         <f t="shared" si="10"/>
-        <v>3.1350000000000003E-2</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
+        <v>1.0345500000000001E-2</v>
+      </c>
+      <c r="N93">
         <f t="shared" si="11"/>
-        <v>1.0345500000000001E-2</v>
-      </c>
-      <c r="N93">
-        <f t="shared" si="12"/>
         <v>-1.0345500000000001E-2</v>
       </c>
       <c r="O93" s="5">
@@ -15662,25 +15676,25 @@
         <v>28</v>
       </c>
       <c r="I94" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>8.8199999999999997E-3</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
+        <f t="shared" si="9"/>
+        <v>2.52E-2</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
         <f t="shared" si="10"/>
-        <v>2.52E-2</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
+        <v>8.3160000000000005E-3</v>
+      </c>
+      <c r="N94">
         <f t="shared" si="11"/>
-        <v>8.3160000000000005E-3</v>
-      </c>
-      <c r="N94">
-        <f t="shared" si="12"/>
         <v>-8.3160000000000005E-3</v>
       </c>
       <c r="O94">
@@ -15710,25 +15724,25 @@
         <v>29</v>
       </c>
       <c r="I95" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>5.5299999999999995E-2</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95">
+        <f t="shared" si="9"/>
+        <v>0.158</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
         <f t="shared" si="10"/>
-        <v>0.158</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
+        <v>5.2139999999999999E-2</v>
+      </c>
+      <c r="N95">
         <f t="shared" si="11"/>
-        <v>5.2139999999999999E-2</v>
-      </c>
-      <c r="N95">
-        <f t="shared" si="12"/>
         <v>-5.2139999999999999E-2</v>
       </c>
       <c r="O95">
@@ -15758,25 +15772,25 @@
         <v>4</v>
       </c>
       <c r="I96" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.47E-2</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
+        <f t="shared" si="9"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
         <f t="shared" si="10"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
+        <v>1.3860000000000001E-2</v>
+      </c>
+      <c r="N96">
         <f t="shared" si="11"/>
-        <v>1.3860000000000001E-2</v>
-      </c>
-      <c r="N96">
-        <f t="shared" si="12"/>
         <v>-1.3860000000000001E-2</v>
       </c>
       <c r="O96" s="5">
@@ -15812,25 +15826,25 @@
         <v>4</v>
       </c>
       <c r="I97" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.1025E-2</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
+        <f t="shared" si="9"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
         <f t="shared" si="10"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N97">
         <f t="shared" si="11"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N97">
-        <f t="shared" si="12"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O97" s="5">
@@ -15866,25 +15880,25 @@
         <v>29</v>
       </c>
       <c r="I98" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.13685</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98">
+        <f t="shared" si="9"/>
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
         <f t="shared" si="10"/>
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
+        <v>0.12903000000000001</v>
+      </c>
+      <c r="N98">
         <f t="shared" si="11"/>
-        <v>0.12903000000000001</v>
-      </c>
-      <c r="N98">
-        <f t="shared" si="12"/>
         <v>-0.12903000000000001</v>
       </c>
       <c r="O98">
@@ -15914,25 +15928,25 @@
         <v>32</v>
       </c>
       <c r="I99" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.14402499999999999</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99">
+        <f t="shared" si="9"/>
+        <v>0.41149999999999998</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
         <f t="shared" si="10"/>
-        <v>0.41149999999999998</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
+        <v>0.13579500000000003</v>
+      </c>
+      <c r="N99">
         <f t="shared" si="11"/>
-        <v>0.13579500000000003</v>
-      </c>
-      <c r="N99">
-        <f t="shared" si="12"/>
         <v>-0.13579500000000003</v>
       </c>
       <c r="O99">
@@ -15962,25 +15976,25 @@
         <v>11</v>
       </c>
       <c r="I100" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.117075</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
+        <f t="shared" si="9"/>
+        <v>0.33450000000000002</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
         <f t="shared" si="10"/>
-        <v>0.33450000000000002</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
+        <v>0.11038500000000001</v>
+      </c>
+      <c r="N100">
         <f t="shared" si="11"/>
-        <v>0.11038500000000001</v>
-      </c>
-      <c r="N100">
-        <f t="shared" si="12"/>
         <v>-0.11038500000000001</v>
       </c>
       <c r="O100">
@@ -16010,25 +16024,25 @@
         <v>25</v>
       </c>
       <c r="I101" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.41475000000000001</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101">
+        <f t="shared" si="9"/>
+        <v>1.1850000000000001</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
         <f t="shared" si="10"/>
-        <v>1.1850000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
+        <v>0.39105000000000001</v>
+      </c>
+      <c r="N101">
         <f t="shared" si="11"/>
-        <v>0.39105000000000001</v>
-      </c>
-      <c r="N101">
-        <f t="shared" si="12"/>
         <v>-0.39105000000000001</v>
       </c>
       <c r="O101">
@@ -16058,25 +16072,25 @@
         <v>17</v>
       </c>
       <c r="I102" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4.7425000000000002E-2</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
+        <f t="shared" si="9"/>
+        <v>0.13550000000000001</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
         <f t="shared" si="10"/>
-        <v>0.13550000000000001</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
+        <v>4.4715000000000005E-2</v>
+      </c>
+      <c r="N102">
         <f t="shared" si="11"/>
-        <v>4.4715000000000005E-2</v>
-      </c>
-      <c r="N102">
-        <f t="shared" si="12"/>
         <v>-4.4715000000000005E-2</v>
       </c>
       <c r="O102">
@@ -16106,25 +16120,25 @@
         <v>6</v>
       </c>
       <c r="I103" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.17587499999999998</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103">
+        <f t="shared" si="9"/>
+        <v>0.50249999999999995</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
         <f t="shared" si="10"/>
-        <v>0.50249999999999995</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
+        <v>0.16582500000000003</v>
+      </c>
+      <c r="N103">
         <f t="shared" si="11"/>
-        <v>0.16582500000000003</v>
-      </c>
-      <c r="N103">
-        <f t="shared" si="12"/>
         <v>-0.16582500000000003</v>
       </c>
       <c r="O103" s="5">
@@ -16160,25 +16174,25 @@
         <v>3</v>
       </c>
       <c r="I104" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.118475</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104">
+        <f t="shared" si="9"/>
+        <v>0.33850000000000002</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
         <f t="shared" si="10"/>
-        <v>0.33850000000000002</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
+        <v>0.111705</v>
+      </c>
+      <c r="N104">
         <f t="shared" si="11"/>
-        <v>0.111705</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="12"/>
         <v>-0.111705</v>
       </c>
       <c r="O104" s="5">
@@ -16214,25 +16228,25 @@
         <v>9</v>
       </c>
       <c r="I105" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>5.1974999999999993E-2</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105">
+        <f t="shared" si="9"/>
+        <v>0.14849999999999999</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
         <f t="shared" si="10"/>
-        <v>0.14849999999999999</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
+        <v>4.9005E-2</v>
+      </c>
+      <c r="N105">
         <f t="shared" si="11"/>
-        <v>4.9005E-2</v>
-      </c>
-      <c r="N105">
-        <f t="shared" si="12"/>
         <v>-4.9005E-2</v>
       </c>
       <c r="O105" s="5">
@@ -16268,25 +16282,25 @@
         <v>34</v>
       </c>
       <c r="I106" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.6624999999999997E-2</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
+        <f t="shared" si="9"/>
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
         <f t="shared" si="10"/>
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
+        <v>1.5675000000000001E-2</v>
+      </c>
+      <c r="N106">
         <f t="shared" si="11"/>
-        <v>1.5675000000000001E-2</v>
-      </c>
-      <c r="N106">
-        <f t="shared" si="12"/>
         <v>-1.5675000000000001E-2</v>
       </c>
       <c r="O106">
@@ -16316,25 +16330,25 @@
         <v>26</v>
       </c>
       <c r="I107" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.3975E-2</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
+        <f t="shared" si="9"/>
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
         <f t="shared" si="10"/>
-        <v>6.8500000000000005E-2</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
+        <v>2.2605E-2</v>
+      </c>
+      <c r="N107">
         <f t="shared" si="11"/>
-        <v>2.2605E-2</v>
-      </c>
-      <c r="N107">
-        <f t="shared" si="12"/>
         <v>-2.2605E-2</v>
       </c>
       <c r="O107">
@@ -16364,25 +16378,25 @@
         <v>22</v>
       </c>
       <c r="I108" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>8.1375000000000003E-2</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
+        <f t="shared" si="9"/>
+        <v>0.23250000000000001</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
         <f t="shared" si="10"/>
-        <v>0.23250000000000001</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
+        <v>7.6725000000000015E-2</v>
+      </c>
+      <c r="N108">
         <f t="shared" si="11"/>
-        <v>7.6725000000000015E-2</v>
-      </c>
-      <c r="N108">
-        <f t="shared" si="12"/>
         <v>-7.6725000000000015E-2</v>
       </c>
       <c r="O108">
@@ -16412,25 +16426,25 @@
         <v>10</v>
       </c>
       <c r="I109" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>6.474999999999999E-3</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
+        <f t="shared" si="9"/>
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
         <f t="shared" si="10"/>
-        <v>1.8499999999999999E-2</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
+        <v>6.1050000000000002E-3</v>
+      </c>
+      <c r="N109">
         <f t="shared" si="11"/>
-        <v>6.1050000000000002E-3</v>
-      </c>
-      <c r="N109">
-        <f t="shared" si="12"/>
         <v>-6.1050000000000002E-3</v>
       </c>
       <c r="O109">
@@ -16467,18 +16481,18 @@
         <v>0</v>
       </c>
       <c r="K110">
+        <f t="shared" si="9"/>
+        <v>5.5E-2</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
         <f t="shared" si="10"/>
-        <v>5.5E-2</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
+        <v>1.8150000000000003E-2</v>
+      </c>
+      <c r="N110">
         <f t="shared" si="11"/>
-        <v>1.8150000000000003E-2</v>
-      </c>
-      <c r="N110">
-        <f t="shared" si="12"/>
         <v>-1.8150000000000003E-2</v>
       </c>
       <c r="O110" s="5">
@@ -16514,25 +16528,25 @@
         <v>4</v>
       </c>
       <c r="I111" s="29">
-        <f t="shared" ref="I111:I125" si="15">0.1*K111</f>
+        <f t="shared" ref="I111:I125" si="14">0.1*K111</f>
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
+        <f t="shared" si="9"/>
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
         <f t="shared" si="10"/>
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
+        <v>1.6830000000000001E-2</v>
+      </c>
+      <c r="N111">
         <f t="shared" si="11"/>
-        <v>1.6830000000000001E-2</v>
-      </c>
-      <c r="N111">
-        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O111" s="5">
@@ -16568,25 +16582,25 @@
         <v>4</v>
       </c>
       <c r="I112" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112">
+        <f t="shared" si="9"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
         <f t="shared" si="10"/>
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
+        <v>1.056E-2</v>
+      </c>
+      <c r="N112">
         <f t="shared" si="11"/>
-        <v>1.056E-2</v>
-      </c>
-      <c r="N112">
-        <f t="shared" si="12"/>
         <v>-1.056E-2</v>
       </c>
       <c r="O112" s="5">
@@ -16622,14 +16636,14 @@
         <v>11</v>
       </c>
       <c r="I113" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2.725E-3</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2.725E-2</v>
       </c>
       <c r="L113">
@@ -16640,7 +16654,7 @@
         <v>8.9925000000000005E-3</v>
       </c>
       <c r="N113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-8.9925000000000005E-3</v>
       </c>
       <c r="O113">
@@ -16670,25 +16684,25 @@
         <v>29</v>
       </c>
       <c r="I114" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.36099999999999999</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
+        <f t="shared" si="9"/>
+        <v>3.61</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
         <f t="shared" si="10"/>
-        <v>3.61</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
+        <v>1.1913</v>
+      </c>
+      <c r="N114">
         <f t="shared" si="11"/>
-        <v>1.1913</v>
-      </c>
-      <c r="N114">
-        <f t="shared" si="12"/>
         <v>-1.1913</v>
       </c>
       <c r="O114">
@@ -16718,25 +16732,25 @@
         <v>32</v>
       </c>
       <c r="I115" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.46445000000000003</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
+        <f t="shared" si="9"/>
+        <v>4.6444999999999999</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
         <f t="shared" si="10"/>
-        <v>4.6444999999999999</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
+        <v>1.5326850000000001</v>
+      </c>
+      <c r="N115">
         <f t="shared" si="11"/>
-        <v>1.5326850000000001</v>
-      </c>
-      <c r="N115">
-        <f t="shared" si="12"/>
         <v>-1.5326850000000001</v>
       </c>
       <c r="O115">
@@ -16766,25 +16780,25 @@
         <v>11</v>
       </c>
       <c r="I116" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.15329999999999999</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
+        <f t="shared" si="9"/>
+        <v>1.5329999999999999</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
         <f t="shared" si="10"/>
-        <v>1.5329999999999999</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
+        <v>0.50589000000000006</v>
+      </c>
+      <c r="N116">
         <f t="shared" si="11"/>
-        <v>0.50589000000000006</v>
-      </c>
-      <c r="N116">
-        <f t="shared" si="12"/>
         <v>-0.50589000000000006</v>
       </c>
       <c r="O116">
@@ -16814,25 +16828,25 @@
         <v>25</v>
       </c>
       <c r="I117" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.17660000000000001</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
+        <f t="shared" si="9"/>
+        <v>1.766</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
         <f t="shared" si="10"/>
-        <v>1.766</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
+        <v>0.58277999999999996</v>
+      </c>
+      <c r="N117">
         <f t="shared" si="11"/>
-        <v>0.58277999999999996</v>
-      </c>
-      <c r="N117">
-        <f t="shared" si="12"/>
         <v>-0.58277999999999996</v>
       </c>
       <c r="O117">
@@ -16862,25 +16876,25 @@
         <v>17</v>
       </c>
       <c r="I118" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.52739999999999998</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
+        <f t="shared" si="9"/>
+        <v>5.274</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
         <f t="shared" si="10"/>
-        <v>5.274</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
+        <v>1.7404200000000001</v>
+      </c>
+      <c r="N118">
         <f t="shared" si="11"/>
-        <v>1.7404200000000001</v>
-      </c>
-      <c r="N118">
-        <f t="shared" si="12"/>
         <v>-1.7404200000000001</v>
       </c>
       <c r="O118">
@@ -16910,25 +16924,25 @@
         <v>6</v>
       </c>
       <c r="I119" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.25714999999999999</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119">
+        <f t="shared" si="9"/>
+        <v>2.5714999999999999</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
         <f t="shared" si="10"/>
-        <v>2.5714999999999999</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
+        <v>0.84859499999999999</v>
+      </c>
+      <c r="N119">
         <f t="shared" si="11"/>
-        <v>0.84859499999999999</v>
-      </c>
-      <c r="N119">
-        <f t="shared" si="12"/>
         <v>-0.84859499999999999</v>
       </c>
       <c r="O119" s="5">
@@ -16964,25 +16978,25 @@
         <v>3</v>
       </c>
       <c r="I120" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.19595000000000001</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120">
+        <f t="shared" si="9"/>
+        <v>1.9595</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
         <f t="shared" si="10"/>
-        <v>1.9595</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
+        <v>0.64663499999999996</v>
+      </c>
+      <c r="N120">
         <f t="shared" si="11"/>
-        <v>0.64663499999999996</v>
-      </c>
-      <c r="N120">
-        <f t="shared" si="12"/>
         <v>-0.64663499999999996</v>
       </c>
       <c r="O120" s="5">
@@ -17018,25 +17032,25 @@
         <v>9</v>
       </c>
       <c r="I121" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.25445000000000001</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121">
+        <f t="shared" si="9"/>
+        <v>2.5445000000000002</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
         <f t="shared" si="10"/>
-        <v>2.5445000000000002</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
+        <v>0.83968500000000001</v>
+      </c>
+      <c r="N121">
         <f t="shared" si="11"/>
-        <v>0.83968500000000001</v>
-      </c>
-      <c r="N121">
-        <f t="shared" si="12"/>
         <v>-0.83968500000000001</v>
       </c>
       <c r="O121" s="5">
@@ -17072,25 +17086,25 @@
         <v>34</v>
       </c>
       <c r="I122" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.31505000000000005</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
+        <f t="shared" si="9"/>
+        <v>3.1505000000000001</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
         <f t="shared" si="10"/>
-        <v>3.1505000000000001</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
+        <v>1.0396650000000001</v>
+      </c>
+      <c r="N122">
         <f t="shared" si="11"/>
-        <v>1.0396650000000001</v>
-      </c>
-      <c r="N122">
-        <f t="shared" si="12"/>
         <v>-1.0396650000000001</v>
       </c>
       <c r="O122">
@@ -17120,25 +17134,25 @@
         <v>26</v>
       </c>
       <c r="I123" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.29694999999999999</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123">
+        <f t="shared" si="9"/>
+        <v>2.9695</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
         <f t="shared" si="10"/>
-        <v>2.9695</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
+        <v>0.97993500000000011</v>
+      </c>
+      <c r="N123">
         <f t="shared" si="11"/>
-        <v>0.97993500000000011</v>
-      </c>
-      <c r="N123">
-        <f t="shared" si="12"/>
         <v>-0.97993500000000011</v>
       </c>
       <c r="O123">
@@ -17168,25 +17182,25 @@
         <v>22</v>
       </c>
       <c r="I124" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.65195000000000003</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124">
+        <f t="shared" si="9"/>
+        <v>6.5194999999999999</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
         <f t="shared" si="10"/>
-        <v>6.5194999999999999</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
+        <v>2.1514349999999998</v>
+      </c>
+      <c r="N124">
         <f t="shared" si="11"/>
-        <v>2.1514349999999998</v>
-      </c>
-      <c r="N124">
-        <f t="shared" si="12"/>
         <v>-2.1514349999999998</v>
       </c>
       <c r="O124">
@@ -17216,25 +17230,25 @@
         <v>10</v>
       </c>
       <c r="I125" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125">
+        <f t="shared" si="9"/>
+        <v>2.13</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
         <f t="shared" si="10"/>
-        <v>2.13</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
+        <v>0.70289999999999997</v>
+      </c>
+      <c r="N125">
         <f t="shared" si="11"/>
-        <v>0.70289999999999997</v>
-      </c>
-      <c r="N125">
-        <f t="shared" si="12"/>
         <v>-0.70289999999999997</v>
       </c>
       <c r="O125">
@@ -17278,11 +17292,11 @@
         <v>0</v>
       </c>
       <c r="M126">
+        <f t="shared" si="10"/>
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="N126">
         <f t="shared" si="11"/>
-        <v>0.12540000000000001</v>
-      </c>
-      <c r="N126">
-        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O126">
@@ -17319,18 +17333,18 @@
         <v>0</v>
       </c>
       <c r="K127">
+        <f t="shared" si="9"/>
+        <v>0.38</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
         <f t="shared" si="10"/>
-        <v>0.38</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="N127">
         <f t="shared" si="11"/>
-        <v>0.12540000000000001</v>
-      </c>
-      <c r="N127">
-        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O127">
@@ -17360,25 +17374,25 @@
         <v>12</v>
       </c>
       <c r="I128" s="28">
-        <f t="shared" ref="I128:I143" si="16">0.35*K128</f>
+        <f t="shared" ref="I128:I143" si="15">0.35*K128</f>
         <v>0.132825</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
+        <f t="shared" si="9"/>
+        <v>0.3795</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
         <f t="shared" si="10"/>
-        <v>0.3795</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
+        <v>0.12523500000000001</v>
+      </c>
+      <c r="N128">
         <f t="shared" si="11"/>
-        <v>0.12523500000000001</v>
-      </c>
-      <c r="N128">
-        <f t="shared" si="12"/>
         <v>-0.12523500000000001</v>
       </c>
       <c r="O128">
@@ -17422,11 +17436,11 @@
         <v>0</v>
       </c>
       <c r="M129">
+        <f t="shared" si="10"/>
+        <v>0.12474</v>
+      </c>
+      <c r="N129">
         <f t="shared" si="11"/>
-        <v>0.12474</v>
-      </c>
-      <c r="N129">
-        <f t="shared" si="12"/>
         <v>-0.12474</v>
       </c>
       <c r="O129">
@@ -17456,25 +17470,25 @@
         <v>12</v>
       </c>
       <c r="I130" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.12249999999999998</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
+        <f t="shared" si="9"/>
+        <v>0.35</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
         <f t="shared" si="10"/>
-        <v>0.35</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
+        <v>0.11550000000000001</v>
+      </c>
+      <c r="N130">
         <f t="shared" si="11"/>
-        <v>0.11550000000000001</v>
-      </c>
-      <c r="N130">
-        <f t="shared" si="12"/>
         <v>-0.11550000000000001</v>
       </c>
       <c r="O130">
@@ -17504,25 +17518,25 @@
         <v>12</v>
       </c>
       <c r="I131" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.10149999999999999</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <f t="shared" ref="K131:K171" si="17">E131/2000</f>
+        <f t="shared" ref="K131:K171" si="16">E131/2000</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131">
+        <f t="shared" si="10"/>
+        <v>9.5700000000000007E-2</v>
+      </c>
+      <c r="N131">
         <f t="shared" si="11"/>
-        <v>9.5700000000000007E-2</v>
-      </c>
-      <c r="N131">
-        <f t="shared" si="12"/>
         <v>-9.5700000000000007E-2</v>
       </c>
       <c r="O131">
@@ -17552,25 +17566,25 @@
         <v>11</v>
       </c>
       <c r="I132" s="28">
+        <f t="shared" si="15"/>
+        <v>0.13159999999999999</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
         <f t="shared" si="16"/>
-        <v>0.13159999999999999</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <f t="shared" si="17"/>
         <v>0.376</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132">
+        <f t="shared" si="10"/>
+        <v>0.12408000000000001</v>
+      </c>
+      <c r="N132">
         <f t="shared" si="11"/>
-        <v>0.12408000000000001</v>
-      </c>
-      <c r="N132">
-        <f t="shared" si="12"/>
         <v>-0.12408000000000001</v>
       </c>
       <c r="O132">
@@ -17600,25 +17614,25 @@
         <v>11</v>
       </c>
       <c r="I133" s="28">
+        <f t="shared" si="15"/>
+        <v>0.1280125</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
         <f t="shared" si="16"/>
-        <v>0.1280125</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <f t="shared" si="17"/>
         <v>0.36575000000000002</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133">
+        <f t="shared" si="10"/>
+        <v>0.1206975</v>
+      </c>
+      <c r="N133">
         <f t="shared" si="11"/>
-        <v>0.1206975</v>
-      </c>
-      <c r="N133">
-        <f t="shared" si="12"/>
         <v>-0.1206975</v>
       </c>
       <c r="O133">
@@ -17648,25 +17662,25 @@
         <v>11</v>
       </c>
       <c r="I134" s="28">
+        <f t="shared" si="15"/>
+        <v>3.3249999999999998E-3</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
         <f t="shared" si="16"/>
-        <v>3.3249999999999998E-3</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <f t="shared" si="17"/>
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="M134">
+        <f t="shared" si="10"/>
+        <v>3.1350000000000002E-3</v>
+      </c>
+      <c r="N134">
         <f t="shared" si="11"/>
-        <v>3.1350000000000002E-3</v>
-      </c>
-      <c r="N134">
-        <f t="shared" si="12"/>
         <v>-3.1350000000000002E-3</v>
       </c>
       <c r="O134">
@@ -17703,18 +17717,18 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
+      <c r="N135">
         <f t="shared" si="11"/>
-        <v>0.33</v>
-      </c>
-      <c r="N135">
-        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O135">
@@ -17744,25 +17758,25 @@
         <v>11</v>
       </c>
       <c r="I136" s="37">
-        <f t="shared" ref="I136:I140" si="18">0.35*K136*0.9</f>
+        <f t="shared" ref="I136:I140" si="17">0.35*K136*0.9</f>
         <v>0.315</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
+      <c r="N136">
         <f t="shared" si="11"/>
-        <v>0.33</v>
-      </c>
-      <c r="N136">
-        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O136">
@@ -17792,25 +17806,25 @@
         <v>28</v>
       </c>
       <c r="I137" s="37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.315</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
+      <c r="N137">
         <f t="shared" si="11"/>
-        <v>0.33</v>
-      </c>
-      <c r="N137">
-        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O137">
@@ -17840,25 +17854,25 @@
         <v>22</v>
       </c>
       <c r="I138" s="37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.47249999999999992</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.5</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138">
+        <f t="shared" si="10"/>
+        <v>0.495</v>
+      </c>
+      <c r="N138">
         <f t="shared" si="11"/>
-        <v>0.495</v>
-      </c>
-      <c r="N138">
-        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O138">
@@ -17888,25 +17902,25 @@
         <v>22</v>
       </c>
       <c r="I139" s="37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.47249999999999992</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.5</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139">
+        <f t="shared" si="10"/>
+        <v>0.495</v>
+      </c>
+      <c r="N139">
         <f t="shared" si="11"/>
-        <v>0.495</v>
-      </c>
-      <c r="N139">
-        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O139">
@@ -17936,21 +17950,21 @@
         <v>21</v>
       </c>
       <c r="I140" s="37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.63</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140">
-        <f t="shared" ref="M140:M171" si="19">0.33*E140/2000</f>
+        <f t="shared" ref="M140:M171" si="18">0.33*E140/2000</f>
         <v>0.66</v>
       </c>
       <c r="N140">
@@ -17984,21 +17998,21 @@
         <v>51</v>
       </c>
       <c r="I141" s="28">
+        <f t="shared" si="15"/>
+        <v>1.3999999999999999E-2</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
         <f t="shared" si="16"/>
-        <v>1.3999999999999999E-2</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <f t="shared" si="17"/>
         <v>0.04</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1.3200000000000002E-2</v>
       </c>
       <c r="N141">
@@ -18032,21 +18046,21 @@
         <v>25</v>
       </c>
       <c r="I142" s="28">
+        <f t="shared" si="15"/>
+        <v>1.0499999999999999E-2</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
         <f t="shared" si="16"/>
-        <v>1.0499999999999999E-2</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <f t="shared" si="17"/>
         <v>0.03</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N142">
@@ -18080,25 +18094,25 @@
         <v>47</v>
       </c>
       <c r="I143" s="28">
+        <f t="shared" si="15"/>
+        <v>8.7499999999999991E-3</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
         <f t="shared" si="16"/>
-        <v>8.7499999999999991E-3</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <f t="shared" si="17"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N143">
-        <f t="shared" ref="N143:N171" si="20">-M143</f>
+        <f t="shared" ref="N143:N171" si="19">-M143</f>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O143">
@@ -18135,18 +18149,18 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4.4499999999999998E-2</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144">
+        <f t="shared" si="18"/>
+        <v>1.4685E-2</v>
+      </c>
+      <c r="N144">
         <f t="shared" si="19"/>
-        <v>1.4685E-2</v>
-      </c>
-      <c r="N144">
-        <f t="shared" si="20"/>
         <v>-1.4685E-2</v>
       </c>
       <c r="O144">
@@ -18176,25 +18190,25 @@
         <v>25</v>
       </c>
       <c r="I145" s="29">
-        <f t="shared" ref="I145:I171" si="21">0.1*K145</f>
+        <f t="shared" ref="I145:I171" si="20">0.1*K145</f>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.75E-2</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145">
+        <f t="shared" si="18"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N145">
         <f t="shared" si="19"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N145">
-        <f t="shared" si="20"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O145">
@@ -18224,25 +18238,25 @@
         <v>25</v>
       </c>
       <c r="I146" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>7.4000000000000003E-3</v>
       </c>
       <c r="J146">
         <v>0</v>
       </c>
       <c r="K146">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="L146">
         <v>0</v>
       </c>
       <c r="M146">
+        <f t="shared" si="18"/>
+        <v>2.4420000000000001E-2</v>
+      </c>
+      <c r="N146">
         <f t="shared" si="19"/>
-        <v>2.4420000000000001E-2</v>
-      </c>
-      <c r="N146">
-        <f t="shared" si="20"/>
         <v>-2.4420000000000001E-2</v>
       </c>
       <c r="O146">
@@ -18272,25 +18286,25 @@
         <v>46</v>
       </c>
       <c r="I147" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.5000000000000005E-3</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
       <c r="M147">
+        <f t="shared" si="18"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N147">
         <f t="shared" si="19"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N147">
-        <f t="shared" si="20"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O147">
@@ -18320,25 +18334,25 @@
         <v>16</v>
       </c>
       <c r="I148" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0.04</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
       <c r="M148">
+        <f t="shared" si="18"/>
+        <v>1.3200000000000002E-2</v>
+      </c>
+      <c r="N148">
         <f t="shared" si="19"/>
-        <v>1.3200000000000002E-2</v>
-      </c>
-      <c r="N148">
-        <f t="shared" si="20"/>
         <v>-1.3200000000000002E-2</v>
       </c>
       <c r="O148">
@@ -18368,25 +18382,25 @@
         <v>45</v>
       </c>
       <c r="I149" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.0500000000000002E-3</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.0499999999999999E-2</v>
       </c>
       <c r="L149">
         <v>0</v>
       </c>
       <c r="M149">
+        <f t="shared" si="18"/>
+        <v>1.0065000000000001E-2</v>
+      </c>
+      <c r="N149">
         <f t="shared" si="19"/>
-        <v>1.0065000000000001E-2</v>
-      </c>
-      <c r="N149">
-        <f t="shared" si="20"/>
         <v>-1.0065000000000001E-2</v>
       </c>
       <c r="O149">
@@ -18423,18 +18437,18 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="L150">
         <v>0</v>
       </c>
       <c r="M150">
+        <f t="shared" si="18"/>
+        <v>1.221E-2</v>
+      </c>
+      <c r="N150">
         <f t="shared" si="19"/>
-        <v>1.221E-2</v>
-      </c>
-      <c r="N150">
-        <f t="shared" si="20"/>
         <v>-1.221E-2</v>
       </c>
       <c r="O150">
@@ -18464,25 +18478,25 @@
         <v>23</v>
       </c>
       <c r="I151" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J151">
         <v>0</v>
       </c>
       <c r="K151">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.75E-2</v>
       </c>
       <c r="L151">
         <v>0</v>
       </c>
       <c r="M151">
+        <f t="shared" si="18"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N151">
         <f t="shared" si="19"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N151">
-        <f t="shared" si="20"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O151">
@@ -18512,25 +18526,25 @@
         <v>20</v>
       </c>
       <c r="I152" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.75E-2</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
       <c r="M152">
+        <f t="shared" si="18"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N152">
         <f t="shared" si="19"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N152">
-        <f t="shared" si="20"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O152">
@@ -18560,25 +18574,25 @@
         <v>19</v>
       </c>
       <c r="I153" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="L153">
         <v>0</v>
       </c>
       <c r="M153">
+        <f t="shared" si="18"/>
+        <v>1.2375000000000001E-2</v>
+      </c>
+      <c r="N153">
         <f t="shared" si="19"/>
-        <v>1.2375000000000001E-2</v>
-      </c>
-      <c r="N153">
-        <f t="shared" si="20"/>
         <v>-1.2375000000000001E-2</v>
       </c>
       <c r="O153">
@@ -18608,25 +18622,25 @@
         <v>30</v>
       </c>
       <c r="I154" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="J154">
         <v>0</v>
       </c>
       <c r="K154">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.7E-2</v>
       </c>
       <c r="L154">
         <v>0</v>
       </c>
       <c r="M154">
+        <f t="shared" si="18"/>
+        <v>8.9099999999999995E-3</v>
+      </c>
+      <c r="N154">
         <f t="shared" si="19"/>
-        <v>8.9099999999999995E-3</v>
-      </c>
-      <c r="N154">
-        <f t="shared" si="20"/>
         <v>-8.9099999999999995E-3</v>
       </c>
       <c r="O154">
@@ -18656,25 +18670,25 @@
         <v>9</v>
       </c>
       <c r="I155" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.2500000000000003E-3</v>
       </c>
       <c r="J155">
         <v>0</v>
       </c>
       <c r="K155">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="L155">
         <v>0</v>
       </c>
       <c r="M155">
+        <f t="shared" si="18"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N155">
         <f t="shared" si="19"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N155">
-        <f t="shared" si="20"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O155" s="5">
@@ -18710,25 +18724,25 @@
         <v>50</v>
       </c>
       <c r="I156" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.1000000000000003E-3</v>
       </c>
       <c r="J156">
         <v>0</v>
       </c>
       <c r="K156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.1E-2</v>
       </c>
       <c r="L156">
         <v>0</v>
       </c>
       <c r="M156">
+        <f t="shared" si="18"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N156">
         <f t="shared" si="19"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N156">
-        <f t="shared" si="20"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O156">
@@ -18758,25 +18772,25 @@
         <v>27</v>
       </c>
       <c r="I157" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="J157">
         <v>0</v>
       </c>
       <c r="K157">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4.7E-2</v>
       </c>
       <c r="L157">
         <v>0</v>
       </c>
       <c r="M157">
+        <f t="shared" si="18"/>
+        <v>1.5510000000000001E-2</v>
+      </c>
+      <c r="N157">
         <f t="shared" si="19"/>
-        <v>1.5510000000000001E-2</v>
-      </c>
-      <c r="N157">
-        <f t="shared" si="20"/>
         <v>-1.5510000000000001E-2</v>
       </c>
       <c r="O157">
@@ -18806,25 +18820,25 @@
         <v>20</v>
       </c>
       <c r="I158" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>4.8000000000000004E-3</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
       <c r="K158">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="L158">
         <v>0</v>
       </c>
       <c r="M158">
+        <f t="shared" si="18"/>
+        <v>1.584E-2</v>
+      </c>
+      <c r="N158">
         <f t="shared" si="19"/>
-        <v>1.584E-2</v>
-      </c>
-      <c r="N158">
-        <f t="shared" si="20"/>
         <v>-1.584E-2</v>
       </c>
       <c r="O158">
@@ -18854,25 +18868,25 @@
         <v>27</v>
       </c>
       <c r="I159" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>4.3E-3</v>
       </c>
       <c r="J159">
         <v>0</v>
       </c>
       <c r="K159">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="L159">
         <v>0</v>
       </c>
       <c r="M159">
+        <f t="shared" si="18"/>
+        <v>1.4190000000000001E-2</v>
+      </c>
+      <c r="N159">
         <f t="shared" si="19"/>
-        <v>1.4190000000000001E-2</v>
-      </c>
-      <c r="N159">
-        <f t="shared" si="20"/>
         <v>-1.4190000000000001E-2</v>
       </c>
       <c r="O159">
@@ -18902,25 +18916,25 @@
         <v>47</v>
       </c>
       <c r="I160" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>6.6000000000000008E-3</v>
       </c>
       <c r="J160">
         <v>0</v>
       </c>
       <c r="K160">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="L160">
         <v>0</v>
       </c>
       <c r="M160">
+        <f t="shared" si="18"/>
+        <v>2.1780000000000001E-2</v>
+      </c>
+      <c r="N160">
         <f t="shared" si="19"/>
-        <v>2.1780000000000001E-2</v>
-      </c>
-      <c r="N160">
-        <f t="shared" si="20"/>
         <v>-2.1780000000000001E-2</v>
       </c>
       <c r="O160">
@@ -18950,25 +18964,25 @@
         <v>48</v>
       </c>
       <c r="I161" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.2500000000000003E-3</v>
       </c>
       <c r="J161">
         <v>0</v>
       </c>
       <c r="K161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="L161">
         <v>0</v>
       </c>
       <c r="M161">
+        <f t="shared" si="18"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N161">
         <f t="shared" si="19"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N161">
-        <f t="shared" si="20"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O161">
@@ -18998,25 +19012,25 @@
         <v>27</v>
       </c>
       <c r="I162" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>5.8000000000000005E-3</v>
       </c>
       <c r="J162">
         <v>0</v>
       </c>
       <c r="K162">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="L162">
         <v>0</v>
       </c>
       <c r="M162">
+        <f t="shared" si="18"/>
+        <v>1.9140000000000001E-2</v>
+      </c>
+      <c r="N162">
         <f t="shared" si="19"/>
-        <v>1.9140000000000001E-2</v>
-      </c>
-      <c r="N162">
-        <f t="shared" si="20"/>
         <v>-1.9140000000000001E-2</v>
       </c>
       <c r="O162">
@@ -19046,25 +19060,25 @@
         <v>9</v>
       </c>
       <c r="I163" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.15E-3</v>
       </c>
       <c r="J163">
         <v>0</v>
       </c>
       <c r="K163">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.15E-2</v>
       </c>
       <c r="L163">
         <v>0</v>
       </c>
       <c r="M163">
+        <f t="shared" si="18"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N163">
         <f t="shared" si="19"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N163">
-        <f t="shared" si="20"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O163" s="5">
@@ -19100,25 +19114,25 @@
         <v>48</v>
       </c>
       <c r="I164" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.9000000000000002E-3</v>
       </c>
       <c r="J164">
         <v>0</v>
       </c>
       <c r="K164">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="L164">
         <v>0</v>
       </c>
       <c r="M164">
+        <f t="shared" si="18"/>
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N164">
         <f t="shared" si="19"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N164">
-        <f t="shared" si="20"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O164">
@@ -19148,25 +19162,25 @@
         <v>20</v>
       </c>
       <c r="I165" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>5.7500000000000008E-3</v>
       </c>
       <c r="J165">
         <v>0</v>
       </c>
       <c r="K165">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>5.7500000000000002E-2</v>
       </c>
       <c r="L165">
         <v>0</v>
       </c>
       <c r="M165">
+        <f t="shared" si="18"/>
+        <v>1.8975000000000002E-2</v>
+      </c>
+      <c r="N165">
         <f t="shared" si="19"/>
-        <v>1.8975000000000002E-2</v>
-      </c>
-      <c r="N165">
-        <f t="shared" si="20"/>
         <v>-1.8975000000000002E-2</v>
       </c>
       <c r="O165">
@@ -19196,25 +19210,25 @@
         <v>5</v>
       </c>
       <c r="I166" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="J166">
         <v>0</v>
       </c>
       <c r="K166">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="L166">
         <v>0</v>
       </c>
       <c r="M166">
+        <f t="shared" si="18"/>
+        <v>1.7819999999999999E-2</v>
+      </c>
+      <c r="N166">
         <f t="shared" si="19"/>
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="N166">
-        <f t="shared" si="20"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O166" s="5">
@@ -19250,25 +19264,25 @@
         <v>3</v>
       </c>
       <c r="I167" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.65E-3</v>
       </c>
       <c r="J167">
         <v>0</v>
       </c>
       <c r="K167">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.6499999999999999E-2</v>
       </c>
       <c r="L167">
         <v>0</v>
       </c>
       <c r="M167">
+        <f t="shared" si="18"/>
+        <v>8.745000000000001E-3</v>
+      </c>
+      <c r="N167">
         <f t="shared" si="19"/>
-        <v>8.745000000000001E-3</v>
-      </c>
-      <c r="N167">
-        <f t="shared" si="20"/>
         <v>-8.745000000000001E-3</v>
       </c>
       <c r="O167" s="5">
@@ -19304,25 +19318,25 @@
         <v>19</v>
       </c>
       <c r="I168" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.9000000000000002E-3</v>
       </c>
       <c r="J168">
         <v>0</v>
       </c>
       <c r="K168">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="L168">
         <v>0</v>
       </c>
       <c r="M168">
+        <f t="shared" si="18"/>
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N168">
         <f t="shared" si="19"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N168">
-        <f t="shared" si="20"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O168">
@@ -19352,25 +19366,25 @@
         <v>31</v>
       </c>
       <c r="I169" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>3.1000000000000003E-3</v>
       </c>
       <c r="J169">
         <v>0</v>
       </c>
       <c r="K169">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3.1E-2</v>
       </c>
       <c r="L169">
         <v>0</v>
       </c>
       <c r="M169">
+        <f t="shared" si="18"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N169">
         <f t="shared" si="19"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N169">
-        <f t="shared" si="20"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O169">
@@ -19400,25 +19414,25 @@
         <v>31</v>
       </c>
       <c r="I170" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>6.8000000000000005E-3</v>
       </c>
       <c r="J170">
         <v>0</v>
       </c>
       <c r="K170">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="L170">
         <v>0</v>
       </c>
       <c r="M170">
+        <f t="shared" si="18"/>
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="N170">
         <f t="shared" si="19"/>
-        <v>2.2440000000000002E-2</v>
-      </c>
-      <c r="N170">
-        <f t="shared" si="20"/>
         <v>-2.2440000000000002E-2</v>
       </c>
       <c r="O170">
@@ -19449,25 +19463,25 @@
       </c>
       <c r="H171" s="10"/>
       <c r="I171" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.9499999999999999E-3</v>
       </c>
       <c r="J171" s="10">
         <v>0</v>
       </c>
       <c r="K171">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2.9499999999999998E-2</v>
       </c>
       <c r="L171" s="10">
         <v>0</v>
       </c>
       <c r="M171">
+        <f t="shared" si="18"/>
+        <v>9.7350000000000006E-3</v>
+      </c>
+      <c r="N171">
         <f t="shared" si="19"/>
-        <v>9.7350000000000006E-3</v>
-      </c>
-      <c r="N171">
-        <f t="shared" si="20"/>
         <v>-9.7350000000000006E-3</v>
       </c>
       <c r="O171" s="5">
@@ -19570,7 +19584,7 @@
         <v>272</v>
       </c>
       <c r="E2">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -19579,18 +19593,18 @@
         <v>40</v>
       </c>
       <c r="I2" s="32">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <f>1.972/2</f>
-        <v>0.98599999999999999</v>
+        <f>E2/2000</f>
+        <v>1.17</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-0.98599999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -27983,7 +27997,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="J2">
         <v>380</v>
@@ -28027,7 +28041,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="J3">
         <v>380</v>
@@ -28071,7 +28085,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="J4">
         <v>380</v>
@@ -28115,7 +28129,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="J5">
         <v>380</v>
@@ -28159,7 +28173,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="J6">
         <v>380</v>
@@ -28203,7 +28217,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="J7">
         <v>380</v>
@@ -28247,7 +28261,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>10800</v>
       </c>
       <c r="J8">
         <v>380</v>
@@ -28291,7 +28305,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="J9">
         <v>380</v>
@@ -28337,7 +28351,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10">
-        <v>700</v>
+        <v>11100</v>
       </c>
       <c r="J10" s="10">
         <v>380</v>
@@ -31584,8 +31598,8 @@
       </c>
       <c r="G83" s="24"/>
       <c r="H83" s="24"/>
-      <c r="I83" s="24">
-        <v>1972</v>
+      <c r="I83">
+        <v>2340</v>
       </c>
       <c r="J83" s="24">
         <v>380</v>

--- a/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
+++ b/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A20821-9A7B-4D69-8EB5-6322CD6D2AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387CA65E-D1FD-43C1-909A-9FFE1F8AAAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="1905" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23925" yWindow="2925" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -7809,10 +7809,10 @@
       </c>
       <c r="Z2">
         <f>AA2/2</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AA2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB2">
         <v>0.33</v>
@@ -7897,10 +7897,10 @@
       </c>
       <c r="Z3">
         <f>AA3/2</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB3">
         <v>0.33</v>

--- a/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
+++ b/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387CA65E-D1FD-43C1-909A-9FFE1F8AAAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2002FC36-5E3A-4883-8D8A-124FFE4A23A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23925" yWindow="2925" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -7809,10 +7809,10 @@
       </c>
       <c r="Z2">
         <f>AA2/2</f>
+        <v>1.5</v>
+      </c>
+      <c r="AA2">
         <v>3</v>
-      </c>
-      <c r="AA2">
-        <v>6</v>
       </c>
       <c r="AB2">
         <v>0.33</v>
@@ -7897,10 +7897,10 @@
       </c>
       <c r="Z3">
         <f>AA3/2</f>
+        <v>1.5</v>
+      </c>
+      <c r="AA3">
         <v>3</v>
-      </c>
-      <c r="AA3">
-        <v>6</v>
       </c>
       <c r="AB3">
         <v>0.33</v>
@@ -10779,12 +10779,10 @@
         <v>380</v>
       </c>
       <c r="G37" s="35">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H37" s="32">
-        <f>TAN(ACOS(0.95))*G37</f>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -10807,12 +10805,10 @@
         <v>380</v>
       </c>
       <c r="G38" s="35">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H38" s="32">
-        <f t="shared" ref="H38:H46" si="0">TAN(ACOS(0.95))*G38</f>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -10835,12 +10831,10 @@
         <v>380</v>
       </c>
       <c r="G39" s="35">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H39" s="32">
-        <f t="shared" si="0"/>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -10863,12 +10857,10 @@
         <v>380</v>
       </c>
       <c r="G40" s="35">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H40" s="32">
-        <f t="shared" si="0"/>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -10891,12 +10883,10 @@
         <v>380</v>
       </c>
       <c r="G41" s="35">
-        <f>0.261034-0.05+0.18</f>
-        <v>0.39103399999999999</v>
+        <v>0.26103399999999999</v>
       </c>
       <c r="H41" s="32">
-        <f t="shared" si="0"/>
-        <v>0.1285266603845116</v>
+        <v>8.5797726711259376E-2</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -10919,12 +10909,10 @@
         <v>380</v>
       </c>
       <c r="G42" s="35">
-        <f>0.211034+0.18</f>
-        <v>0.39103399999999999</v>
+        <v>0.211034</v>
       </c>
       <c r="H42" s="32">
-        <f t="shared" si="0"/>
-        <v>0.1285266603845116</v>
+        <v>6.9363521452316224E-2</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -10947,12 +10935,10 @@
         <v>380</v>
       </c>
       <c r="G43" s="32">
-        <f>1.79</f>
-        <v>1.79</v>
+        <v>0.05</v>
       </c>
       <c r="H43" s="32">
-        <f t="shared" si="0"/>
-        <v>0.58834454827016514</v>
+        <v>1.6434205258943162E-2</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -10975,12 +10961,10 @@
         <v>380</v>
       </c>
       <c r="G44" s="35">
-        <f>0.10199-0.05+0.12</f>
-        <v>0.17198999999999998</v>
+        <v>0.10199</v>
       </c>
       <c r="H44" s="32">
-        <f t="shared" si="0"/>
-        <v>5.6530379249712673E-2</v>
+        <v>3.3522491887192259E-2</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -11003,12 +10987,10 @@
         <v>380</v>
       </c>
       <c r="G45" s="32">
-        <f>0.05-0.05+2.05</f>
-        <v>2.0499999999999998</v>
+        <v>0.05</v>
       </c>
       <c r="H45" s="32">
-        <f t="shared" si="0"/>
-        <v>0.67380241561666954</v>
+        <v>1.6434205258943162E-2</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -11031,12 +11013,10 @@
         <v>380</v>
       </c>
       <c r="G46" s="35">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H46" s="32">
-        <f t="shared" si="0"/>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -11130,7 +11110,7 @@
         <v>263</v>
       </c>
       <c r="E2">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -11139,18 +11119,19 @@
         <v>38</v>
       </c>
       <c r="I2" s="32">
-        <v>0.24</v>
+        <f>0.1/2</f>
+        <v>0.05</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
         <f>E2/2000</f>
-        <v>1.17</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-1.17</v>
+        <v>-0.98599999999999999</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -11178,7 +11159,7 @@
         <v>264</v>
       </c>
       <c r="E3">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="F3">
         <v>380</v>
@@ -11187,25 +11168,26 @@
         <v>39</v>
       </c>
       <c r="I3" s="32">
-        <v>0.24</v>
+        <f t="shared" ref="I3:I7" si="0">0.1/2</f>
+        <v>0.05</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K66" si="0">E3/2000</f>
-        <v>1.17</v>
+        <f t="shared" ref="K3:K66" si="1">E3/2000</f>
+        <v>0.98599999999999999</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L10" si="1">-K3</f>
-        <v>-1.17</v>
+        <f t="shared" ref="L3:L10" si="2">-K3</f>
+        <v>-0.98599999999999999</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M10" si="2">5/2</f>
+        <f t="shared" ref="M3:M10" si="3">5/2</f>
         <v>2.5</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N10" si="3">-M3</f>
+        <f t="shared" ref="N3:N10" si="4">-M3</f>
         <v>-2.5</v>
       </c>
       <c r="O3">
@@ -11226,7 +11208,7 @@
         <v>265</v>
       </c>
       <c r="E4">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="F4">
         <v>380</v>
@@ -11235,25 +11217,26 @@
         <v>41</v>
       </c>
       <c r="I4" s="32">
-        <v>0.24</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>1.17</v>
+        <f t="shared" si="1"/>
+        <v>0.49299999999999999</v>
       </c>
       <c r="L4">
-        <f t="shared" si="1"/>
-        <v>-1.17</v>
+        <f t="shared" si="2"/>
+        <v>-0.49299999999999999</v>
       </c>
       <c r="M4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O4">
@@ -11274,7 +11257,7 @@
         <v>266</v>
       </c>
       <c r="E5">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="F5">
         <v>380</v>
@@ -11283,25 +11266,26 @@
         <v>42</v>
       </c>
       <c r="I5" s="32">
-        <v>0.24</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
-        <v>1.17</v>
+        <f t="shared" si="1"/>
+        <v>0.49299999999999999</v>
       </c>
       <c r="L5">
-        <f t="shared" si="1"/>
-        <v>-1.17</v>
+        <f t="shared" si="2"/>
+        <v>-0.49299999999999999</v>
       </c>
       <c r="M5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O5">
@@ -11322,7 +11306,7 @@
         <v>267</v>
       </c>
       <c r="E6">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="F6">
         <v>380</v>
@@ -11331,25 +11315,26 @@
         <v>43</v>
       </c>
       <c r="I6" s="32">
-        <v>0.18</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.56399999999999995</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <f t="shared" si="2"/>
+        <v>-0.56399999999999995</v>
       </c>
       <c r="M6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O6">
@@ -11370,7 +11355,7 @@
         <v>268</v>
       </c>
       <c r="E7">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="F7">
         <v>380</v>
@@ -11379,25 +11364,26 @@
         <v>44</v>
       </c>
       <c r="I7" s="32">
-        <v>0.18</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.56399999999999995</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <f t="shared" si="2"/>
+        <v>-0.56399999999999995</v>
       </c>
       <c r="M7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O7">
@@ -11418,7 +11404,7 @@
         <v>269</v>
       </c>
       <c r="E8">
-        <v>10800</v>
+        <v>1000</v>
       </c>
       <c r="F8">
         <v>380</v>
@@ -11427,26 +11413,26 @@
         <v>35</v>
       </c>
       <c r="I8" s="35">
-        <f>0.100864/2 - 0.05 + 1.79</f>
-        <v>1.790432</v>
+        <f>0.100864/2</f>
+        <v>5.0431999999999998E-2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
-        <v>5.4</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>-5.4</v>
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
       </c>
       <c r="M8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O8">
@@ -11467,7 +11453,7 @@
         <v>270</v>
       </c>
       <c r="E9">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F9">
         <v>380</v>
@@ -11476,26 +11462,26 @@
         <v>36</v>
       </c>
       <c r="I9" s="32">
-        <f>0.12</f>
-        <v>0.12</v>
+        <f>0.1/2</f>
+        <v>0.05</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.35</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <f t="shared" si="2"/>
+        <v>-0.35</v>
       </c>
       <c r="M9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O9">
@@ -11516,7 +11502,7 @@
         <v>271</v>
       </c>
       <c r="E10" s="10">
-        <v>11100</v>
+        <v>700</v>
       </c>
       <c r="F10" s="10">
         <v>380</v>
@@ -11526,26 +11512,26 @@
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="35">
-        <f>0.49222/2 - 0.05 + 2.05</f>
-        <v>2.2461099999999998</v>
+        <f>0.49222/2</f>
+        <v>0.24611</v>
       </c>
       <c r="J10" s="10">
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
-        <v>5.55</v>
+        <f t="shared" si="1"/>
+        <v>0.35</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="1"/>
-        <v>-5.55</v>
+        <f t="shared" si="2"/>
+        <v>-0.35</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O10" s="10">
@@ -11586,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="L11">
@@ -11627,25 +11613,25 @@
         <v>28</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I14" si="4">0.6*E12/2000</f>
+        <f t="shared" ref="I12:I14" si="5">0.6*E12/2000</f>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" ref="M12:M75" si="5">0.33*E12/2000</f>
+        <f t="shared" ref="M12:M75" si="6">0.33*E12/2000</f>
         <v>2.0625000000000001E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:N13" si="6">-M12</f>
+        <f t="shared" ref="N12:N13" si="7">-M12</f>
         <v>-2.0625000000000001E-2</v>
       </c>
       <c r="O12">
@@ -11675,25 +11661,25 @@
         <v>29</v>
       </c>
       <c r="I13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1000000000000003E-3</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.155E-3</v>
       </c>
       <c r="N13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.155E-3</v>
       </c>
       <c r="O13">
@@ -11723,25 +11709,25 @@
         <v>12</v>
       </c>
       <c r="I14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.14E-2</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.9E-2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.2700000000000004E-3</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:N77" si="7">-M14</f>
+        <f t="shared" ref="N14:N77" si="8">-M14</f>
         <v>-6.2700000000000004E-3</v>
       </c>
       <c r="O14">
@@ -11778,18 +11764,18 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.24249999999999999</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.0024999999999999E-2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-8.0024999999999999E-2</v>
       </c>
       <c r="O15">
@@ -11826,18 +11812,18 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4E-2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.92E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-7.92E-3</v>
       </c>
       <c r="O16" s="5">
@@ -11873,25 +11859,25 @@
         <v>11</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I80" si="8">0.6*E17/2000</f>
+        <f t="shared" ref="I17:I80" si="9">0.6*E17/2000</f>
         <v>0.13650000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.22750000000000001</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.5075000000000003E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-7.5075000000000003E-2</v>
       </c>
       <c r="O17">
@@ -11921,25 +11907,25 @@
         <v>28</v>
       </c>
       <c r="I18">
+        <f t="shared" si="9"/>
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="6"/>
+        <v>0.13926000000000002</v>
+      </c>
+      <c r="N18">
         <f t="shared" si="8"/>
-        <v>0.25319999999999998</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>0.42199999999999999</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="5"/>
-        <v>0.13926000000000002</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="7"/>
         <v>-0.13926000000000002</v>
       </c>
       <c r="O18">
@@ -11969,25 +11955,25 @@
         <v>3</v>
       </c>
       <c r="I19">
+        <f t="shared" si="9"/>
+        <v>2.1599999999999998E-2</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="6"/>
+        <v>1.188E-2</v>
+      </c>
+      <c r="N19">
         <f t="shared" si="8"/>
-        <v>2.1599999999999998E-2</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="5"/>
-        <v>1.188E-2</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O19" s="5">
@@ -12023,25 +12009,25 @@
         <v>3</v>
       </c>
       <c r="I20">
+        <f t="shared" si="9"/>
+        <v>2.1599999999999998E-2</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="6"/>
+        <v>1.188E-2</v>
+      </c>
+      <c r="N20">
         <f t="shared" si="8"/>
-        <v>2.1599999999999998E-2</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="5"/>
-        <v>1.188E-2</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O20" s="5">
@@ -12077,25 +12063,25 @@
         <v>6</v>
       </c>
       <c r="I21">
+        <f t="shared" si="9"/>
+        <v>3.9299999999999995E-2</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>6.5500000000000003E-2</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="6"/>
+        <v>2.1615000000000002E-2</v>
+      </c>
+      <c r="N21">
         <f t="shared" si="8"/>
-        <v>3.9299999999999995E-2</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="0"/>
-        <v>6.5500000000000003E-2</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="5"/>
-        <v>2.1615000000000002E-2</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="7"/>
         <v>-2.1615000000000002E-2</v>
       </c>
       <c r="O21" s="5">
@@ -12131,25 +12117,25 @@
         <v>6</v>
       </c>
       <c r="I22">
+        <f t="shared" si="9"/>
+        <v>0.1077</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="6"/>
+        <v>5.9234999999999996E-2</v>
+      </c>
+      <c r="N22">
         <f t="shared" si="8"/>
-        <v>0.1077</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>0.17949999999999999</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="5"/>
-        <v>5.9234999999999996E-2</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O22" s="5">
@@ -12185,25 +12171,25 @@
         <v>6</v>
       </c>
       <c r="I23">
+        <f t="shared" si="9"/>
+        <v>0.1077</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="6"/>
+        <v>5.9234999999999996E-2</v>
+      </c>
+      <c r="N23">
         <f t="shared" si="8"/>
-        <v>0.1077</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>0.17949999999999999</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="5"/>
-        <v>5.9234999999999996E-2</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O23" s="5">
@@ -12239,25 +12225,25 @@
         <v>6</v>
       </c>
       <c r="I24">
+        <f t="shared" si="9"/>
+        <v>0.10829999999999999</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>0.18049999999999999</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="6"/>
+        <v>5.9565000000000007E-2</v>
+      </c>
+      <c r="N24">
         <f t="shared" si="8"/>
-        <v>0.10829999999999999</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="0"/>
-        <v>0.18049999999999999</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="5"/>
-        <v>5.9565000000000007E-2</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="7"/>
         <v>-5.9565000000000007E-2</v>
       </c>
       <c r="O24" s="5">
@@ -12293,25 +12279,25 @@
         <v>18</v>
       </c>
       <c r="I25">
+        <f t="shared" si="9"/>
+        <v>0.1077</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="6"/>
+        <v>5.9234999999999996E-2</v>
+      </c>
+      <c r="N25">
         <f t="shared" si="8"/>
-        <v>0.1077</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="0"/>
-        <v>0.17949999999999999</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="5"/>
-        <v>5.9234999999999996E-2</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O25">
@@ -12341,25 +12327,25 @@
         <v>18</v>
       </c>
       <c r="I26">
+        <f t="shared" si="9"/>
+        <v>0.108</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="6"/>
+        <v>5.9400000000000008E-2</v>
+      </c>
+      <c r="N26">
         <f t="shared" si="8"/>
-        <v>0.108</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="0"/>
-        <v>0.18</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="5"/>
-        <v>5.9400000000000008E-2</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="7"/>
         <v>-5.9400000000000008E-2</v>
       </c>
       <c r="O26">
@@ -12389,25 +12375,25 @@
         <v>25</v>
       </c>
       <c r="I27">
+        <f t="shared" si="9"/>
+        <v>0.1278</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="6"/>
+        <v>7.0290000000000005E-2</v>
+      </c>
+      <c r="N27">
         <f t="shared" si="8"/>
-        <v>0.1278</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="0"/>
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="5"/>
-        <v>7.0290000000000005E-2</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O27">
@@ -12437,25 +12423,25 @@
         <v>25</v>
       </c>
       <c r="I28">
+        <f t="shared" si="9"/>
+        <v>0.1245</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>0.20749999999999999</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="6"/>
+        <v>6.8475000000000008E-2</v>
+      </c>
+      <c r="N28">
         <f t="shared" si="8"/>
-        <v>0.1245</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="0"/>
-        <v>0.20749999999999999</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="5"/>
-        <v>6.8475000000000008E-2</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O28">
@@ -12485,25 +12471,25 @@
         <v>13</v>
       </c>
       <c r="I29">
+        <f t="shared" si="9"/>
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="6"/>
+        <v>1.3695000000000001E-2</v>
+      </c>
+      <c r="N29">
         <f t="shared" si="8"/>
-        <v>2.4899999999999999E-2</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="0"/>
-        <v>4.1500000000000002E-2</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="5"/>
-        <v>1.3695000000000001E-2</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="7"/>
         <v>-1.3695000000000001E-2</v>
       </c>
       <c r="O29">
@@ -12533,25 +12519,25 @@
         <v>33</v>
       </c>
       <c r="I30">
+        <f t="shared" si="9"/>
+        <v>3.3600000000000005E-2</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="6"/>
+        <v>1.848E-2</v>
+      </c>
+      <c r="N30">
         <f t="shared" si="8"/>
-        <v>3.3600000000000005E-2</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="0"/>
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="5"/>
-        <v>1.848E-2</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="7"/>
         <v>-1.848E-2</v>
       </c>
       <c r="O30">
@@ -12581,25 +12567,25 @@
         <v>24</v>
       </c>
       <c r="I31">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999989E-3</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="6"/>
+        <v>3.96E-3</v>
+      </c>
+      <c r="N31">
         <f t="shared" si="8"/>
-        <v>7.1999999999999989E-3</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <f t="shared" si="5"/>
-        <v>3.96E-3</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O31">
@@ -12629,25 +12615,25 @@
         <v>24</v>
       </c>
       <c r="I32">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999989E-3</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="6"/>
+        <v>3.96E-3</v>
+      </c>
+      <c r="N32">
         <f t="shared" si="8"/>
-        <v>7.1999999999999989E-3</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <f t="shared" si="5"/>
-        <v>3.96E-3</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O32">
@@ -12677,25 +12663,25 @@
         <v>24</v>
       </c>
       <c r="I33">
+        <f t="shared" si="9"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>0.11</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="6"/>
+        <v>3.6300000000000006E-2</v>
+      </c>
+      <c r="N33">
         <f t="shared" si="8"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="0"/>
-        <v>0.11</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <f t="shared" si="5"/>
-        <v>3.6300000000000006E-2</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="7"/>
         <v>-3.6300000000000006E-2</v>
       </c>
       <c r="O33">
@@ -12725,25 +12711,25 @@
         <v>28</v>
       </c>
       <c r="I34">
+        <f t="shared" si="9"/>
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>3.95E-2</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="6"/>
+        <v>1.3035E-2</v>
+      </c>
+      <c r="N34">
         <f t="shared" si="8"/>
-        <v>2.3699999999999999E-2</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="0"/>
-        <v>3.95E-2</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="5"/>
-        <v>1.3035E-2</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="7"/>
         <v>-1.3035E-2</v>
       </c>
       <c r="O34">
@@ -12773,25 +12759,25 @@
         <v>11</v>
       </c>
       <c r="I35">
+        <f t="shared" si="9"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>0.2175</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="6"/>
+        <v>7.1775000000000005E-2</v>
+      </c>
+      <c r="N35">
         <f t="shared" si="8"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="0"/>
-        <v>0.2175</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="5"/>
-        <v>7.1775000000000005E-2</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O35">
@@ -12821,25 +12807,25 @@
         <v>11</v>
       </c>
       <c r="I36">
+        <f t="shared" si="9"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>0.2175</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="6"/>
+        <v>7.1775000000000005E-2</v>
+      </c>
+      <c r="N36">
         <f t="shared" si="8"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="0"/>
-        <v>0.2175</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <f t="shared" si="5"/>
-        <v>7.1775000000000005E-2</v>
-      </c>
-      <c r="N36">
-        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O36">
@@ -12869,25 +12855,25 @@
         <v>22</v>
       </c>
       <c r="I37">
+        <f t="shared" si="9"/>
+        <v>0.18</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="6"/>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="8"/>
-        <v>0.18</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <f t="shared" si="5"/>
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="7"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O37">
@@ -12917,25 +12903,25 @@
         <v>23</v>
       </c>
       <c r="I38">
+        <f t="shared" si="9"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="6"/>
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="N38">
         <f t="shared" si="8"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="0"/>
-        <v>0.03</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <f t="shared" si="5"/>
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="N38">
-        <f t="shared" si="7"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O38">
@@ -12965,25 +12951,25 @@
         <v>8</v>
       </c>
       <c r="I39">
+        <f t="shared" si="9"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>0.09</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="6"/>
+        <v>2.9700000000000004E-2</v>
+      </c>
+      <c r="N39">
         <f t="shared" si="8"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="0"/>
-        <v>0.09</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <f t="shared" si="5"/>
-        <v>2.9700000000000004E-2</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="7"/>
         <v>-2.9700000000000004E-2</v>
       </c>
       <c r="O39" s="5">
@@ -13019,25 +13005,25 @@
         <v>26</v>
       </c>
       <c r="I40">
+        <f t="shared" si="9"/>
+        <v>0.192</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>0.32</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="6"/>
+        <v>0.10560000000000001</v>
+      </c>
+      <c r="N40">
         <f t="shared" si="8"/>
-        <v>0.192</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <f t="shared" si="0"/>
-        <v>0.32</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <f t="shared" si="5"/>
-        <v>0.10560000000000001</v>
-      </c>
-      <c r="N40">
-        <f t="shared" si="7"/>
         <v>-0.10560000000000001</v>
       </c>
       <c r="O40">
@@ -13067,25 +13053,25 @@
         <v>26</v>
       </c>
       <c r="I41">
+        <f t="shared" si="9"/>
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="6"/>
+        <v>0.21037500000000001</v>
+      </c>
+      <c r="N41">
         <f t="shared" si="8"/>
-        <v>0.38250000000000001</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <f t="shared" si="0"/>
-        <v>0.63749999999999996</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <f t="shared" si="5"/>
-        <v>0.21037500000000001</v>
-      </c>
-      <c r="N41">
-        <f t="shared" si="7"/>
         <v>-0.21037500000000001</v>
       </c>
       <c r="O41">
@@ -13115,25 +13101,25 @@
         <v>8</v>
       </c>
       <c r="I42">
+        <f t="shared" si="9"/>
+        <v>0.105</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="6"/>
+        <v>5.7750000000000003E-2</v>
+      </c>
+      <c r="N42">
         <f t="shared" si="8"/>
-        <v>0.105</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <f t="shared" si="5"/>
-        <v>5.7750000000000003E-2</v>
-      </c>
-      <c r="N42">
-        <f t="shared" si="7"/>
         <v>-5.7750000000000003E-2</v>
       </c>
       <c r="O42" s="5">
@@ -13169,25 +13155,25 @@
         <v>9</v>
       </c>
       <c r="I43">
+        <f t="shared" si="9"/>
+        <v>1.89E-2</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="1"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="6"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N43">
         <f t="shared" si="8"/>
-        <v>1.89E-2</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <f t="shared" si="0"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <f t="shared" si="5"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N43">
-        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O43" s="5">
@@ -13223,25 +13209,25 @@
         <v>9</v>
       </c>
       <c r="I44">
+        <f t="shared" si="9"/>
+        <v>1.89E-2</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="1"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="6"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N44">
         <f t="shared" si="8"/>
-        <v>1.89E-2</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <f t="shared" si="0"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <f t="shared" si="5"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N44">
-        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O44" s="5">
@@ -13277,25 +13263,25 @@
         <v>26</v>
       </c>
       <c r="I45">
+        <f t="shared" si="9"/>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="1"/>
+        <v>0.115</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="6"/>
+        <v>3.7950000000000005E-2</v>
+      </c>
+      <c r="N45">
         <f t="shared" si="8"/>
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <f t="shared" si="0"/>
-        <v>0.115</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="5"/>
-        <v>3.7950000000000005E-2</v>
-      </c>
-      <c r="N45">
-        <f t="shared" si="7"/>
         <v>-3.7950000000000005E-2</v>
       </c>
       <c r="O45">
@@ -13325,25 +13311,25 @@
         <v>30</v>
       </c>
       <c r="I46">
+        <f t="shared" si="9"/>
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="6"/>
+        <v>5.4450000000000002E-3</v>
+      </c>
+      <c r="N46">
         <f t="shared" si="8"/>
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <f t="shared" si="0"/>
-        <v>1.6500000000000001E-2</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="5"/>
-        <v>5.4450000000000002E-3</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="7"/>
         <v>-5.4450000000000002E-3</v>
       </c>
       <c r="O46">
@@ -13373,25 +13359,25 @@
         <v>16</v>
       </c>
       <c r="I47">
+        <f t="shared" si="9"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="6"/>
+        <v>4.1250000000000002E-3</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="8"/>
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="5"/>
-        <v>4.1250000000000002E-3</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="7"/>
         <v>-4.1250000000000002E-3</v>
       </c>
       <c r="O47">
@@ -13421,25 +13407,25 @@
         <v>22</v>
       </c>
       <c r="I48">
+        <f t="shared" si="9"/>
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="6"/>
+        <v>5.28E-3</v>
+      </c>
+      <c r="N48">
         <f t="shared" si="8"/>
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <f t="shared" si="0"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="5"/>
-        <v>5.28E-3</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="7"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O48">
@@ -13469,25 +13455,25 @@
         <v>2</v>
       </c>
       <c r="I49">
+        <f t="shared" si="9"/>
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="1"/>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="6"/>
+        <v>2.112E-2</v>
+      </c>
+      <c r="N49">
         <f t="shared" si="8"/>
-        <v>3.8399999999999997E-2</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <f t="shared" si="0"/>
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="5"/>
-        <v>2.112E-2</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="7"/>
         <v>-2.112E-2</v>
       </c>
       <c r="O49" s="5">
@@ -13523,25 +13509,25 @@
         <v>15</v>
       </c>
       <c r="I50">
+        <f t="shared" si="9"/>
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="1"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="6"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N50">
         <f t="shared" si="8"/>
-        <v>1.8599999999999998E-2</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <f t="shared" si="0"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="5"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="7"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O50">
@@ -13571,25 +13557,25 @@
         <v>15</v>
       </c>
       <c r="I51">
+        <f t="shared" si="9"/>
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="1"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="6"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="8"/>
-        <v>1.6500000000000001E-2</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <f t="shared" si="0"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <f t="shared" si="5"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="7"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O51">
@@ -13619,25 +13605,25 @@
         <v>15</v>
       </c>
       <c r="I52">
+        <f t="shared" si="9"/>
+        <v>7.4700000000000003E-2</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="1"/>
+        <v>0.1245</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="6"/>
+        <v>4.1085000000000003E-2</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="8"/>
-        <v>7.4700000000000003E-2</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <f t="shared" si="0"/>
-        <v>0.1245</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <f t="shared" si="5"/>
-        <v>4.1085000000000003E-2</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="7"/>
         <v>-4.1085000000000003E-2</v>
       </c>
       <c r="O52">
@@ -13667,25 +13653,25 @@
         <v>12</v>
       </c>
       <c r="I53">
+        <f t="shared" si="9"/>
+        <v>4.3199999999999995E-2</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="1"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="6"/>
+        <v>2.376E-2</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="8"/>
-        <v>4.3199999999999995E-2</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <f t="shared" si="5"/>
-        <v>2.376E-2</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="7"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O53">
@@ -13715,25 +13701,25 @@
         <v>10</v>
       </c>
       <c r="I54">
+        <f t="shared" si="9"/>
+        <v>7.4399999999999994E-2</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="1"/>
+        <v>0.124</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="6"/>
+        <v>4.0920000000000005E-2</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="8"/>
-        <v>7.4399999999999994E-2</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <f t="shared" si="0"/>
-        <v>0.124</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <f t="shared" si="5"/>
-        <v>4.0920000000000005E-2</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="7"/>
         <v>-4.0920000000000005E-2</v>
       </c>
       <c r="O54">
@@ -13763,25 +13749,25 @@
         <v>10</v>
       </c>
       <c r="I55">
+        <f t="shared" si="9"/>
+        <v>3.0899999999999997E-2</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="1"/>
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="6"/>
+        <v>1.6995E-2</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="8"/>
-        <v>3.0899999999999997E-2</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <f t="shared" si="0"/>
-        <v>5.1499999999999997E-2</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <f t="shared" si="5"/>
-        <v>1.6995E-2</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="7"/>
         <v>-1.6995E-2</v>
       </c>
       <c r="O55">
@@ -13811,25 +13797,25 @@
         <v>10</v>
       </c>
       <c r="I56">
+        <f t="shared" si="9"/>
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="1"/>
+        <v>0.1125</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="6"/>
+        <v>3.7124999999999998E-2</v>
+      </c>
+      <c r="N56">
         <f t="shared" si="8"/>
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <f t="shared" si="0"/>
-        <v>0.1125</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <f t="shared" si="5"/>
-        <v>3.7124999999999998E-2</v>
-      </c>
-      <c r="N56">
-        <f t="shared" si="7"/>
         <v>-3.7124999999999998E-2</v>
       </c>
       <c r="O56">
@@ -13859,25 +13845,25 @@
         <v>15</v>
       </c>
       <c r="I57">
+        <f t="shared" si="9"/>
+        <v>2.0099999999999996E-2</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="1"/>
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="6"/>
+        <v>1.1054999999999999E-2</v>
+      </c>
+      <c r="N57">
         <f t="shared" si="8"/>
-        <v>2.0099999999999996E-2</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <f t="shared" si="0"/>
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <f t="shared" si="5"/>
-        <v>1.1054999999999999E-2</v>
-      </c>
-      <c r="N57">
-        <f t="shared" si="7"/>
         <v>-1.1054999999999999E-2</v>
       </c>
       <c r="O57">
@@ -13907,25 +13893,25 @@
         <v>12</v>
       </c>
       <c r="I58">
+        <f t="shared" si="9"/>
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="6"/>
+        <v>7.5900000000000009E-2</v>
+      </c>
+      <c r="N58">
         <f t="shared" si="8"/>
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <f t="shared" si="0"/>
-        <v>0.23</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <f t="shared" si="5"/>
-        <v>7.5900000000000009E-2</v>
-      </c>
-      <c r="N58">
-        <f t="shared" si="7"/>
         <v>-7.5900000000000009E-2</v>
       </c>
       <c r="O58">
@@ -13955,25 +13941,25 @@
         <v>12</v>
       </c>
       <c r="I59">
+        <f t="shared" si="9"/>
+        <v>0.114</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="1"/>
+        <v>0.19</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="6"/>
+        <v>6.2700000000000006E-2</v>
+      </c>
+      <c r="N59">
         <f t="shared" si="8"/>
-        <v>0.114</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <f t="shared" si="0"/>
-        <v>0.19</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <f t="shared" si="5"/>
-        <v>6.2700000000000006E-2</v>
-      </c>
-      <c r="N59">
-        <f t="shared" si="7"/>
         <v>-6.2700000000000006E-2</v>
       </c>
       <c r="O59">
@@ -14003,25 +13989,25 @@
         <v>29</v>
       </c>
       <c r="I60">
+        <f t="shared" si="9"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="1"/>
+        <v>0.22</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="6"/>
+        <v>7.2600000000000012E-2</v>
+      </c>
+      <c r="N60">
         <f t="shared" si="8"/>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <f t="shared" si="0"/>
-        <v>0.22</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <f t="shared" si="5"/>
-        <v>7.2600000000000012E-2</v>
-      </c>
-      <c r="N60">
-        <f t="shared" si="7"/>
         <v>-7.2600000000000012E-2</v>
       </c>
       <c r="O60">
@@ -14051,25 +14037,25 @@
         <v>28</v>
       </c>
       <c r="I61">
+        <f t="shared" si="9"/>
+        <v>0.1278</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="1"/>
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="6"/>
+        <v>7.0290000000000005E-2</v>
+      </c>
+      <c r="N61">
         <f t="shared" si="8"/>
-        <v>0.1278</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <f t="shared" si="0"/>
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <f t="shared" si="5"/>
-        <v>7.0290000000000005E-2</v>
-      </c>
-      <c r="N61">
-        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O61">
@@ -14099,25 +14085,25 @@
         <v>22</v>
       </c>
       <c r="I62">
+        <f t="shared" si="9"/>
+        <v>0.10529999999999999</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="1"/>
+        <v>0.17549999999999999</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="6"/>
+        <v>5.7915000000000008E-2</v>
+      </c>
+      <c r="N62">
         <f t="shared" si="8"/>
-        <v>0.10529999999999999</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <f t="shared" si="0"/>
-        <v>0.17549999999999999</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <f t="shared" si="5"/>
-        <v>5.7915000000000008E-2</v>
-      </c>
-      <c r="N62">
-        <f t="shared" si="7"/>
         <v>-5.7915000000000008E-2</v>
       </c>
       <c r="O62">
@@ -14147,25 +14133,25 @@
         <v>22</v>
       </c>
       <c r="I63">
+        <f t="shared" si="9"/>
+        <v>0.1245</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="1"/>
+        <v>0.20749999999999999</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="6"/>
+        <v>6.8475000000000008E-2</v>
+      </c>
+      <c r="N63">
         <f t="shared" si="8"/>
-        <v>0.1245</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <f t="shared" si="0"/>
-        <v>0.20749999999999999</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <f t="shared" si="5"/>
-        <v>6.8475000000000008E-2</v>
-      </c>
-      <c r="N63">
-        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O63">
@@ -14195,25 +14181,25 @@
         <v>30</v>
       </c>
       <c r="I64">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999989E-3</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="6"/>
+        <v>3.96E-3</v>
+      </c>
+      <c r="N64">
         <f t="shared" si="8"/>
-        <v>7.1999999999999989E-3</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <f t="shared" si="5"/>
-        <v>3.96E-3</v>
-      </c>
-      <c r="N64">
-        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O64">
@@ -14243,25 +14229,25 @@
         <v>21</v>
       </c>
       <c r="I65">
+        <f t="shared" si="9"/>
+        <v>0.13109999999999999</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="1"/>
+        <v>0.2185</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="6"/>
+        <v>7.2105000000000002E-2</v>
+      </c>
+      <c r="N65">
         <f t="shared" si="8"/>
-        <v>0.13109999999999999</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <f t="shared" si="0"/>
-        <v>0.2185</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <f t="shared" si="5"/>
-        <v>7.2105000000000002E-2</v>
-      </c>
-      <c r="N65">
-        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O65">
@@ -14291,25 +14277,25 @@
         <v>21</v>
       </c>
       <c r="I66">
+        <f t="shared" si="9"/>
+        <v>0.13109999999999999</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="1"/>
+        <v>0.2185</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="6"/>
+        <v>7.2105000000000002E-2</v>
+      </c>
+      <c r="N66">
         <f t="shared" si="8"/>
-        <v>0.13109999999999999</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <f t="shared" si="0"/>
-        <v>0.2185</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <f t="shared" si="5"/>
-        <v>7.2105000000000002E-2</v>
-      </c>
-      <c r="N66">
-        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O66">
@@ -14339,25 +14325,25 @@
         <v>21</v>
       </c>
       <c r="I67">
+        <f t="shared" si="9"/>
+        <v>0.13109999999999999</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K130" si="10">E67/2000</f>
+        <v>0.2185</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="6"/>
+        <v>7.2105000000000002E-2</v>
+      </c>
+      <c r="N67">
         <f t="shared" si="8"/>
-        <v>0.13109999999999999</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <f t="shared" ref="K67:K130" si="9">E67/2000</f>
-        <v>0.2185</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <f t="shared" si="5"/>
-        <v>7.2105000000000002E-2</v>
-      </c>
-      <c r="N67">
-        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O67">
@@ -14387,25 +14373,25 @@
         <v>15</v>
       </c>
       <c r="I68">
+        <f t="shared" si="9"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="10"/>
+        <v>0.2175</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="6"/>
+        <v>7.1775000000000005E-2</v>
+      </c>
+      <c r="N68">
         <f t="shared" si="8"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="9"/>
-        <v>0.2175</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <f t="shared" si="5"/>
-        <v>7.1775000000000005E-2</v>
-      </c>
-      <c r="N68">
-        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O68">
@@ -14435,25 +14421,25 @@
         <v>22</v>
       </c>
       <c r="I69">
+        <f t="shared" si="9"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="10"/>
+        <v>0.06</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="6"/>
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="N69">
         <f t="shared" si="8"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <f t="shared" si="9"/>
-        <v>0.06</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <f t="shared" si="5"/>
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="N69">
-        <f t="shared" si="7"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O69">
@@ -14483,25 +14469,25 @@
         <v>22</v>
       </c>
       <c r="I70">
+        <f t="shared" si="9"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="10"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="6"/>
+        <v>5.94E-3</v>
+      </c>
+      <c r="N70">
         <f t="shared" si="8"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <f t="shared" si="9"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <f t="shared" si="5"/>
-        <v>5.94E-3</v>
-      </c>
-      <c r="N70">
-        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O70">
@@ -14531,25 +14517,25 @@
         <v>23</v>
       </c>
       <c r="I71">
+        <f t="shared" si="9"/>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="10"/>
+        <v>1.15E-2</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="6"/>
+        <v>3.7950000000000002E-3</v>
+      </c>
+      <c r="N71">
         <f t="shared" si="8"/>
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <f t="shared" si="9"/>
-        <v>1.15E-2</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <f t="shared" si="5"/>
-        <v>3.7950000000000002E-3</v>
-      </c>
-      <c r="N71">
-        <f t="shared" si="7"/>
         <v>-3.7950000000000002E-3</v>
       </c>
       <c r="O71">
@@ -14579,25 +14565,25 @@
         <v>8</v>
       </c>
       <c r="I72">
+        <f t="shared" si="9"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="10"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="6"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N72">
         <f t="shared" si="8"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <f t="shared" si="5"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N72">
-        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O72" s="5">
@@ -14633,25 +14619,25 @@
         <v>51</v>
       </c>
       <c r="I73">
+        <f t="shared" si="9"/>
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="10"/>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="6"/>
+        <v>2.0130000000000002E-2</v>
+      </c>
+      <c r="N73">
         <f t="shared" si="8"/>
-        <v>3.6600000000000001E-2</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <f t="shared" si="9"/>
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <f t="shared" si="5"/>
-        <v>2.0130000000000002E-2</v>
-      </c>
-      <c r="N73">
-        <f t="shared" si="7"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O73">
@@ -14681,25 +14667,25 @@
         <v>17</v>
       </c>
       <c r="I74">
+        <f t="shared" si="9"/>
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="10"/>
+        <v>1.55E-2</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="6"/>
+        <v>5.1150000000000006E-3</v>
+      </c>
+      <c r="N74">
         <f t="shared" si="8"/>
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <f t="shared" si="9"/>
-        <v>1.55E-2</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <f t="shared" si="5"/>
-        <v>5.1150000000000006E-3</v>
-      </c>
-      <c r="N74">
-        <f t="shared" si="7"/>
         <v>-5.1150000000000006E-3</v>
       </c>
       <c r="O74">
@@ -14729,25 +14715,25 @@
         <v>23</v>
       </c>
       <c r="I75">
+        <f t="shared" si="9"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="10"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="6"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N75">
         <f t="shared" si="8"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <f t="shared" si="5"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N75">
-        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O75">
@@ -14777,25 +14763,25 @@
         <v>8</v>
       </c>
       <c r="I76">
+        <f t="shared" si="9"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="10"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <f t="shared" ref="M76:M139" si="11">0.33*E76/2000</f>
+        <v>5.94E-3</v>
+      </c>
+      <c r="N76">
         <f t="shared" si="8"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <f t="shared" si="9"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <f t="shared" ref="M76:M139" si="10">0.33*E76/2000</f>
-        <v>5.94E-3</v>
-      </c>
-      <c r="N76">
-        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O76" s="5">
@@ -14831,25 +14817,25 @@
         <v>12</v>
       </c>
       <c r="I77">
+        <f t="shared" si="9"/>
+        <v>1.95E-2</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="10"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="11"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N77">
         <f t="shared" si="8"/>
-        <v>1.95E-2</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <f t="shared" si="9"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <f t="shared" si="10"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N77">
-        <f t="shared" si="7"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O77">
@@ -14879,25 +14865,25 @@
         <v>14</v>
       </c>
       <c r="I78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6E-2</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.28E-3</v>
       </c>
       <c r="N78">
-        <f t="shared" ref="N78:N139" si="11">-M78</f>
+        <f t="shared" ref="N78:N139" si="12">-M78</f>
         <v>-5.28E-3</v>
       </c>
       <c r="O78">
@@ -14927,25 +14913,25 @@
         <v>29</v>
       </c>
       <c r="I79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4750000000000001E-2</v>
       </c>
       <c r="N79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.4750000000000001E-2</v>
       </c>
       <c r="O79">
@@ -14975,25 +14961,25 @@
         <v>51</v>
       </c>
       <c r="I80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N80">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O80">
@@ -15023,25 +15009,25 @@
         <v>50</v>
       </c>
       <c r="I81">
-        <f t="shared" ref="I81:I82" si="12">0.6*E81/2000</f>
+        <f t="shared" ref="I81:I82" si="13">0.6*E81/2000</f>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6E-2</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
       <c r="M81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.28E-3</v>
       </c>
       <c r="N81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O81">
@@ -15072,25 +15058,25 @@
       </c>
       <c r="H82" s="10"/>
       <c r="I82">
+        <f t="shared" si="13"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="10"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L82" s="10">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="11"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N82">
         <f t="shared" si="12"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L82" s="10">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <f t="shared" si="10"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N82">
-        <f t="shared" si="11"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O82" s="10">
@@ -15131,18 +15117,18 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="N83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O83">
@@ -15172,25 +15158,25 @@
         <v>13</v>
       </c>
       <c r="I84" s="28">
-        <f t="shared" ref="I84:I109" si="13">0.35*K84</f>
+        <f t="shared" ref="I84:I109" si="14">0.35*K84</f>
         <v>2.2574999999999998E-2</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.4500000000000002E-2</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
       <c r="M84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.1285000000000002E-2</v>
       </c>
       <c r="N84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.1285000000000002E-2</v>
       </c>
       <c r="O84">
@@ -15220,25 +15206,25 @@
         <v>12</v>
       </c>
       <c r="I85" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.0999999999999998E-2</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.06</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
       <c r="M85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="N85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O85">
@@ -15268,25 +15254,25 @@
         <v>12</v>
       </c>
       <c r="I86" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.89E-2</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7819999999999999E-2</v>
       </c>
       <c r="N86">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O86">
@@ -15316,25 +15302,25 @@
         <v>15</v>
       </c>
       <c r="I87" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.1349999999999997E-2</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0130000000000002E-2</v>
       </c>
       <c r="N87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O87">
@@ -15364,25 +15350,25 @@
         <v>6</v>
       </c>
       <c r="I88" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.9925E-2</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.5500000000000007E-2</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8215E-2</v>
       </c>
       <c r="N88">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.8215E-2</v>
       </c>
       <c r="O88" s="5">
@@ -15418,25 +15404,25 @@
         <v>5</v>
       </c>
       <c r="I89" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.5199999999999997E-2</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.376E-2</v>
       </c>
       <c r="N89">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O89" s="5">
@@ -15472,25 +15458,25 @@
         <v>5</v>
       </c>
       <c r="I90" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.9874999999999996E-2</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14249999999999999</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
       <c r="M90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.7025000000000004E-2</v>
       </c>
       <c r="N90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.7025000000000004E-2</v>
       </c>
       <c r="O90" s="5">
@@ -15526,25 +15512,25 @@
         <v>28</v>
       </c>
       <c r="I91" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.7849999999999998E-2</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6830000000000001E-2</v>
       </c>
       <c r="N91">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O91">
@@ -15574,25 +15560,25 @@
         <v>30</v>
       </c>
       <c r="I92" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.4437499999999999E-2</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.1250000000000002E-2</v>
       </c>
       <c r="L92">
         <v>0</v>
       </c>
       <c r="M92">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3612500000000001E-2</v>
       </c>
       <c r="N92">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.3612500000000001E-2</v>
       </c>
       <c r="O92">
@@ -15622,25 +15608,25 @@
         <v>8</v>
       </c>
       <c r="I93" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.09725E-2</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.1350000000000003E-2</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
       <c r="M93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0345500000000001E-2</v>
       </c>
       <c r="N93">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.0345500000000001E-2</v>
       </c>
       <c r="O93" s="5">
@@ -15676,25 +15662,25 @@
         <v>28</v>
       </c>
       <c r="I94" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.8199999999999997E-3</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.52E-2</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="M94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.3160000000000005E-3</v>
       </c>
       <c r="N94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8.3160000000000005E-3</v>
       </c>
       <c r="O94">
@@ -15724,25 +15710,25 @@
         <v>29</v>
       </c>
       <c r="I95" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.5299999999999995E-2</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.158</v>
       </c>
       <c r="L95">
         <v>0</v>
       </c>
       <c r="M95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.2139999999999999E-2</v>
       </c>
       <c r="N95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5.2139999999999999E-2</v>
       </c>
       <c r="O95">
@@ -15772,25 +15758,25 @@
         <v>4</v>
       </c>
       <c r="I96" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.47E-2</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3860000000000001E-2</v>
       </c>
       <c r="N96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.3860000000000001E-2</v>
       </c>
       <c r="O96" s="5">
@@ -15826,25 +15812,25 @@
         <v>4</v>
       </c>
       <c r="I97" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.1025E-2</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.15E-2</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
       <c r="M97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0395000000000001E-2</v>
       </c>
       <c r="N97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O97" s="5">
@@ -15880,25 +15866,25 @@
         <v>29</v>
       </c>
       <c r="I98" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.13685</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.39100000000000001</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="M98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12903000000000001</v>
       </c>
       <c r="N98">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12903000000000001</v>
       </c>
       <c r="O98">
@@ -15928,25 +15914,25 @@
         <v>32</v>
       </c>
       <c r="I99" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.14402499999999999</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.41149999999999998</v>
       </c>
       <c r="L99">
         <v>0</v>
       </c>
       <c r="M99">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.13579500000000003</v>
       </c>
       <c r="N99">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.13579500000000003</v>
       </c>
       <c r="O99">
@@ -15976,25 +15962,25 @@
         <v>11</v>
       </c>
       <c r="I100" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.117075</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.33450000000000002</v>
       </c>
       <c r="L100">
         <v>0</v>
       </c>
       <c r="M100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.11038500000000001</v>
       </c>
       <c r="N100">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.11038500000000001</v>
       </c>
       <c r="O100">
@@ -16024,25 +16010,25 @@
         <v>25</v>
       </c>
       <c r="I101" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.41475000000000001</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1850000000000001</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
       <c r="M101">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.39105000000000001</v>
       </c>
       <c r="N101">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.39105000000000001</v>
       </c>
       <c r="O101">
@@ -16072,25 +16058,25 @@
         <v>17</v>
       </c>
       <c r="I102" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.7425000000000002E-2</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13550000000000001</v>
       </c>
       <c r="L102">
         <v>0</v>
       </c>
       <c r="M102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.4715000000000005E-2</v>
       </c>
       <c r="N102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.4715000000000005E-2</v>
       </c>
       <c r="O102">
@@ -16120,25 +16106,25 @@
         <v>6</v>
       </c>
       <c r="I103" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.17587499999999998</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.50249999999999995</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
       <c r="M103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.16582500000000003</v>
       </c>
       <c r="N103">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.16582500000000003</v>
       </c>
       <c r="O103" s="5">
@@ -16174,25 +16160,25 @@
         <v>3</v>
       </c>
       <c r="I104" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.118475</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.33850000000000002</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
       <c r="M104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.111705</v>
       </c>
       <c r="N104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.111705</v>
       </c>
       <c r="O104" s="5">
@@ -16228,25 +16214,25 @@
         <v>9</v>
       </c>
       <c r="I105" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.1974999999999993E-2</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14849999999999999</v>
       </c>
       <c r="L105">
         <v>0</v>
       </c>
       <c r="M105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.9005E-2</v>
       </c>
       <c r="N105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.9005E-2</v>
       </c>
       <c r="O105" s="5">
@@ -16282,25 +16268,25 @@
         <v>34</v>
       </c>
       <c r="I106" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.6624999999999997E-2</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.7500000000000001E-2</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="M106">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5675000000000001E-2</v>
       </c>
       <c r="N106">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.5675000000000001E-2</v>
       </c>
       <c r="O106">
@@ -16330,25 +16316,25 @@
         <v>26</v>
       </c>
       <c r="I107" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.3975E-2</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="L107">
         <v>0</v>
       </c>
       <c r="M107">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2605E-2</v>
       </c>
       <c r="N107">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.2605E-2</v>
       </c>
       <c r="O107">
@@ -16378,25 +16364,25 @@
         <v>22</v>
       </c>
       <c r="I108" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.1375000000000003E-2</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23250000000000001</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
       <c r="M108">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.6725000000000015E-2</v>
       </c>
       <c r="N108">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7.6725000000000015E-2</v>
       </c>
       <c r="O108">
@@ -16426,25 +16412,25 @@
         <v>10</v>
       </c>
       <c r="I109" s="28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.474999999999999E-3</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8499999999999999E-2</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
       <c r="M109">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1050000000000002E-3</v>
       </c>
       <c r="N109">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6.1050000000000002E-3</v>
       </c>
       <c r="O109">
@@ -16481,18 +16467,18 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.5E-2</v>
       </c>
       <c r="L110">
         <v>0</v>
       </c>
       <c r="M110">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8150000000000003E-2</v>
       </c>
       <c r="N110">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.8150000000000003E-2</v>
       </c>
       <c r="O110" s="5">
@@ -16528,25 +16514,25 @@
         <v>4</v>
       </c>
       <c r="I111" s="29">
-        <f t="shared" ref="I111:I125" si="14">0.1*K111</f>
+        <f t="shared" ref="I111:I125" si="15">0.1*K111</f>
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="L111">
         <v>0</v>
       </c>
       <c r="M111">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6830000000000001E-2</v>
       </c>
       <c r="N111">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O111" s="5">
@@ -16582,25 +16568,25 @@
         <v>4</v>
       </c>
       <c r="I112" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="L112">
         <v>0</v>
       </c>
       <c r="M112">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.056E-2</v>
       </c>
       <c r="N112">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.056E-2</v>
       </c>
       <c r="O112" s="5">
@@ -16636,14 +16622,14 @@
         <v>11</v>
       </c>
       <c r="I113" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.725E-3</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.725E-2</v>
       </c>
       <c r="L113">
@@ -16654,7 +16640,7 @@
         <v>8.9925000000000005E-3</v>
       </c>
       <c r="N113">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8.9925000000000005E-3</v>
       </c>
       <c r="O113">
@@ -16684,25 +16670,25 @@
         <v>29</v>
       </c>
       <c r="I114" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.36099999999999999</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.61</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.1913</v>
       </c>
       <c r="N114">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.1913</v>
       </c>
       <c r="O114">
@@ -16732,25 +16718,25 @@
         <v>32</v>
       </c>
       <c r="I115" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.46445000000000003</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6444999999999999</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="M115">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5326850000000001</v>
       </c>
       <c r="N115">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.5326850000000001</v>
       </c>
       <c r="O115">
@@ -16780,25 +16766,25 @@
         <v>11</v>
       </c>
       <c r="I116" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.15329999999999999</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.5329999999999999</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.50589000000000006</v>
       </c>
       <c r="N116">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.50589000000000006</v>
       </c>
       <c r="O116">
@@ -16828,25 +16814,25 @@
         <v>25</v>
       </c>
       <c r="I117" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.17660000000000001</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.766</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.58277999999999996</v>
       </c>
       <c r="N117">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.58277999999999996</v>
       </c>
       <c r="O117">
@@ -16876,25 +16862,25 @@
         <v>17</v>
       </c>
       <c r="I118" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.52739999999999998</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.274</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="M118">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7404200000000001</v>
       </c>
       <c r="N118">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.7404200000000001</v>
       </c>
       <c r="O118">
@@ -16924,25 +16910,25 @@
         <v>6</v>
       </c>
       <c r="I119" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.25714999999999999</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5714999999999999</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="M119">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.84859499999999999</v>
       </c>
       <c r="N119">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.84859499999999999</v>
       </c>
       <c r="O119" s="5">
@@ -16978,25 +16964,25 @@
         <v>3</v>
       </c>
       <c r="I120" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.19595000000000001</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.9595</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="M120">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.64663499999999996</v>
       </c>
       <c r="N120">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.64663499999999996</v>
       </c>
       <c r="O120" s="5">
@@ -17032,25 +17018,25 @@
         <v>9</v>
       </c>
       <c r="I121" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.25445000000000001</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5445000000000002</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="M121">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.83968500000000001</v>
       </c>
       <c r="N121">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.83968500000000001</v>
       </c>
       <c r="O121" s="5">
@@ -17086,25 +17072,25 @@
         <v>34</v>
       </c>
       <c r="I122" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.31505000000000005</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.1505000000000001</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0396650000000001</v>
       </c>
       <c r="N122">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.0396650000000001</v>
       </c>
       <c r="O122">
@@ -17134,25 +17120,25 @@
         <v>26</v>
       </c>
       <c r="I123" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.29694999999999999</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.9695</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="M123">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.97993500000000011</v>
       </c>
       <c r="N123">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.97993500000000011</v>
       </c>
       <c r="O123">
@@ -17182,25 +17168,25 @@
         <v>22</v>
       </c>
       <c r="I124" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.65195000000000003</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.5194999999999999</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="M124">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.1514349999999998</v>
       </c>
       <c r="N124">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.1514349999999998</v>
       </c>
       <c r="O124">
@@ -17230,25 +17216,25 @@
         <v>10</v>
       </c>
       <c r="I125" s="29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.13</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="M125">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.70289999999999997</v>
       </c>
       <c r="N125">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.70289999999999997</v>
       </c>
       <c r="O125">
@@ -17292,11 +17278,11 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12540000000000001</v>
       </c>
       <c r="N126">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O126">
@@ -17333,18 +17319,18 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
       <c r="M127">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12540000000000001</v>
       </c>
       <c r="N127">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O127">
@@ -17374,25 +17360,25 @@
         <v>12</v>
       </c>
       <c r="I128" s="28">
-        <f t="shared" ref="I128:I143" si="15">0.35*K128</f>
+        <f t="shared" ref="I128:I143" si="16">0.35*K128</f>
         <v>0.132825</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.3795</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12523500000000001</v>
       </c>
       <c r="N128">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12523500000000001</v>
       </c>
       <c r="O128">
@@ -17436,11 +17422,11 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12474</v>
       </c>
       <c r="N129">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12474</v>
       </c>
       <c r="O129">
@@ -17470,25 +17456,25 @@
         <v>12</v>
       </c>
       <c r="I130" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.12249999999999998</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="M130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.11550000000000001</v>
       </c>
       <c r="N130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.11550000000000001</v>
       </c>
       <c r="O130">
@@ -17518,25 +17504,25 @@
         <v>12</v>
       </c>
       <c r="I131" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.10149999999999999</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <f t="shared" ref="K131:K171" si="16">E131/2000</f>
+        <f t="shared" ref="K131:K171" si="17">E131/2000</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.5700000000000007E-2</v>
       </c>
       <c r="N131">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.5700000000000007E-2</v>
       </c>
       <c r="O131">
@@ -17566,25 +17552,25 @@
         <v>11</v>
       </c>
       <c r="I132" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.13159999999999999</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
       <c r="K132">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.376</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12408000000000001</v>
       </c>
       <c r="N132">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12408000000000001</v>
       </c>
       <c r="O132">
@@ -17614,25 +17600,25 @@
         <v>11</v>
       </c>
       <c r="I133" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.1280125</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.36575000000000002</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.1206975</v>
       </c>
       <c r="N133">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.1206975</v>
       </c>
       <c r="O133">
@@ -17662,25 +17648,25 @@
         <v>11</v>
       </c>
       <c r="I134" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.3249999999999998E-3</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="M134">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1350000000000002E-3</v>
       </c>
       <c r="N134">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3.1350000000000002E-3</v>
       </c>
       <c r="O134">
@@ -17717,18 +17703,18 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33</v>
       </c>
       <c r="N135">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O135">
@@ -17758,25 +17744,25 @@
         <v>11</v>
       </c>
       <c r="I136" s="37">
-        <f t="shared" ref="I136:I140" si="17">0.35*K136*0.9</f>
+        <f t="shared" ref="I136:I140" si="18">0.35*K136*0.9</f>
         <v>0.315</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33</v>
       </c>
       <c r="N136">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O136">
@@ -17806,25 +17792,25 @@
         <v>28</v>
       </c>
       <c r="I137" s="37">
+        <f t="shared" si="18"/>
+        <v>0.315</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
         <f t="shared" si="17"/>
-        <v>0.315</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33</v>
       </c>
       <c r="N137">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O137">
@@ -17854,25 +17840,25 @@
         <v>22</v>
       </c>
       <c r="I138" s="37">
+        <f t="shared" si="18"/>
+        <v>0.47249999999999992</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
         <f t="shared" si="17"/>
-        <v>0.47249999999999992</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <f t="shared" si="16"/>
         <v>1.5</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.495</v>
       </c>
       <c r="N138">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O138">
@@ -17902,25 +17888,25 @@
         <v>22</v>
       </c>
       <c r="I139" s="37">
+        <f t="shared" si="18"/>
+        <v>0.47249999999999992</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
         <f t="shared" si="17"/>
-        <v>0.47249999999999992</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <f t="shared" si="16"/>
         <v>1.5</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.495</v>
       </c>
       <c r="N139">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O139">
@@ -17950,21 +17936,21 @@
         <v>21</v>
       </c>
       <c r="I140" s="37">
+        <f t="shared" si="18"/>
+        <v>0.63</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
         <f t="shared" si="17"/>
-        <v>0.63</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140">
-        <f t="shared" ref="M140:M171" si="18">0.33*E140/2000</f>
+        <f t="shared" ref="M140:M171" si="19">0.33*E140/2000</f>
         <v>0.66</v>
       </c>
       <c r="N140">
@@ -17998,21 +17984,21 @@
         <v>51</v>
       </c>
       <c r="I141" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.3999999999999999E-2</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.04</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.3200000000000002E-2</v>
       </c>
       <c r="N141">
@@ -18046,21 +18032,21 @@
         <v>25</v>
       </c>
       <c r="I142" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.0499999999999999E-2</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.03</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N142">
@@ -18094,25 +18080,25 @@
         <v>47</v>
       </c>
       <c r="I143" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.7499999999999991E-3</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N143">
-        <f t="shared" ref="N143:N171" si="19">-M143</f>
+        <f t="shared" ref="N143:N171" si="20">-M143</f>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O143">
@@ -18149,18 +18135,18 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.4499999999999998E-2</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.4685E-2</v>
       </c>
       <c r="N144">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1.4685E-2</v>
       </c>
       <c r="O144">
@@ -18190,25 +18176,25 @@
         <v>25</v>
       </c>
       <c r="I145" s="29">
-        <f t="shared" ref="I145:I171" si="20">0.1*K145</f>
+        <f t="shared" ref="I145:I171" si="21">0.1*K145</f>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.75E-2</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.0750000000000015E-3</v>
       </c>
       <c r="N145">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O145">
@@ -18238,25 +18224,25 @@
         <v>25</v>
       </c>
       <c r="I146" s="29">
+        <f t="shared" si="21"/>
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <f t="shared" si="17"/>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="19"/>
+        <v>2.4420000000000001E-2</v>
+      </c>
+      <c r="N146">
         <f t="shared" si="20"/>
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <f t="shared" si="16"/>
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <f t="shared" si="18"/>
-        <v>2.4420000000000001E-2</v>
-      </c>
-      <c r="N146">
-        <f t="shared" si="19"/>
         <v>-2.4420000000000001E-2</v>
       </c>
       <c r="O146">
@@ -18286,25 +18272,25 @@
         <v>46</v>
       </c>
       <c r="I147" s="29">
+        <f t="shared" si="21"/>
+        <v>2.5000000000000005E-3</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <f t="shared" si="17"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="19"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N147">
         <f t="shared" si="20"/>
-        <v>2.5000000000000005E-3</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <f t="shared" si="16"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <f t="shared" si="18"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N147">
-        <f t="shared" si="19"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O147">
@@ -18334,25 +18320,25 @@
         <v>16</v>
       </c>
       <c r="I148" s="29">
+        <f t="shared" si="21"/>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <f t="shared" si="17"/>
+        <v>0.04</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="19"/>
+        <v>1.3200000000000002E-2</v>
+      </c>
+      <c r="N148">
         <f t="shared" si="20"/>
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <f t="shared" si="16"/>
-        <v>0.04</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <f t="shared" si="18"/>
-        <v>1.3200000000000002E-2</v>
-      </c>
-      <c r="N148">
-        <f t="shared" si="19"/>
         <v>-1.3200000000000002E-2</v>
       </c>
       <c r="O148">
@@ -18382,25 +18368,25 @@
         <v>45</v>
       </c>
       <c r="I149" s="29">
+        <f t="shared" si="21"/>
+        <v>3.0500000000000002E-3</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <f t="shared" si="17"/>
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <f t="shared" si="19"/>
+        <v>1.0065000000000001E-2</v>
+      </c>
+      <c r="N149">
         <f t="shared" si="20"/>
-        <v>3.0500000000000002E-3</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <f t="shared" si="16"/>
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <f t="shared" si="18"/>
-        <v>1.0065000000000001E-2</v>
-      </c>
-      <c r="N149">
-        <f t="shared" si="19"/>
         <v>-1.0065000000000001E-2</v>
       </c>
       <c r="O149">
@@ -18437,18 +18423,18 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="L150">
         <v>0</v>
       </c>
       <c r="M150">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.221E-2</v>
       </c>
       <c r="N150">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1.221E-2</v>
       </c>
       <c r="O150">
@@ -18478,25 +18464,25 @@
         <v>23</v>
       </c>
       <c r="I151" s="29">
+        <f t="shared" si="21"/>
+        <v>2.7500000000000003E-3</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <f t="shared" si="17"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <f t="shared" si="19"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N151">
         <f t="shared" si="20"/>
-        <v>2.7500000000000003E-3</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <f t="shared" si="16"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151">
-        <f t="shared" si="18"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N151">
-        <f t="shared" si="19"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O151">
@@ -18526,25 +18512,25 @@
         <v>20</v>
       </c>
       <c r="I152" s="29">
+        <f t="shared" si="21"/>
+        <v>2.7500000000000003E-3</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <f t="shared" si="17"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <f t="shared" si="19"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N152">
         <f t="shared" si="20"/>
-        <v>2.7500000000000003E-3</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <f t="shared" si="16"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
-        <f t="shared" si="18"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N152">
-        <f t="shared" si="19"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O152">
@@ -18574,25 +18560,25 @@
         <v>19</v>
       </c>
       <c r="I153" s="29">
+        <f t="shared" si="21"/>
+        <v>3.7499999999999999E-3</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <f t="shared" si="17"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <f t="shared" si="19"/>
+        <v>1.2375000000000001E-2</v>
+      </c>
+      <c r="N153">
         <f t="shared" si="20"/>
-        <v>3.7499999999999999E-3</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <f t="shared" si="16"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
-        <f t="shared" si="18"/>
-        <v>1.2375000000000001E-2</v>
-      </c>
-      <c r="N153">
-        <f t="shared" si="19"/>
         <v>-1.2375000000000001E-2</v>
       </c>
       <c r="O153">
@@ -18622,25 +18608,25 @@
         <v>30</v>
       </c>
       <c r="I154" s="29">
+        <f t="shared" si="21"/>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <f t="shared" si="17"/>
+        <v>2.7E-2</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <f t="shared" si="19"/>
+        <v>8.9099999999999995E-3</v>
+      </c>
+      <c r="N154">
         <f t="shared" si="20"/>
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <f t="shared" si="16"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154">
-        <f t="shared" si="18"/>
-        <v>8.9099999999999995E-3</v>
-      </c>
-      <c r="N154">
-        <f t="shared" si="19"/>
         <v>-8.9099999999999995E-3</v>
       </c>
       <c r="O154">
@@ -18670,25 +18656,25 @@
         <v>9</v>
       </c>
       <c r="I155" s="29">
+        <f t="shared" si="21"/>
+        <v>3.2500000000000003E-3</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <f t="shared" si="17"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <f t="shared" si="19"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N155">
         <f t="shared" si="20"/>
-        <v>3.2500000000000003E-3</v>
-      </c>
-      <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <f t="shared" si="16"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
-        <f t="shared" si="18"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N155">
-        <f t="shared" si="19"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O155" s="5">
@@ -18724,25 +18710,25 @@
         <v>50</v>
       </c>
       <c r="I156" s="29">
+        <f t="shared" si="21"/>
+        <v>3.1000000000000003E-3</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <f t="shared" si="17"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <f t="shared" si="19"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N156">
         <f t="shared" si="20"/>
-        <v>3.1000000000000003E-3</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <f t="shared" si="16"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
-        <f t="shared" si="18"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N156">
-        <f t="shared" si="19"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O156">
@@ -18772,25 +18758,25 @@
         <v>27</v>
       </c>
       <c r="I157" s="29">
+        <f t="shared" si="21"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <f t="shared" si="17"/>
+        <v>4.7E-2</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <f t="shared" si="19"/>
+        <v>1.5510000000000001E-2</v>
+      </c>
+      <c r="N157">
         <f t="shared" si="20"/>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="J157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <f t="shared" si="16"/>
-        <v>4.7E-2</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157">
-        <f t="shared" si="18"/>
-        <v>1.5510000000000001E-2</v>
-      </c>
-      <c r="N157">
-        <f t="shared" si="19"/>
         <v>-1.5510000000000001E-2</v>
       </c>
       <c r="O157">
@@ -18820,25 +18806,25 @@
         <v>20</v>
       </c>
       <c r="I158" s="29">
+        <f t="shared" si="21"/>
+        <v>4.8000000000000004E-3</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <f t="shared" si="17"/>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <f t="shared" si="19"/>
+        <v>1.584E-2</v>
+      </c>
+      <c r="N158">
         <f t="shared" si="20"/>
-        <v>4.8000000000000004E-3</v>
-      </c>
-      <c r="J158">
-        <v>0</v>
-      </c>
-      <c r="K158">
-        <f t="shared" si="16"/>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
-        <f t="shared" si="18"/>
-        <v>1.584E-2</v>
-      </c>
-      <c r="N158">
-        <f t="shared" si="19"/>
         <v>-1.584E-2</v>
       </c>
       <c r="O158">
@@ -18868,25 +18854,25 @@
         <v>27</v>
       </c>
       <c r="I159" s="29">
+        <f t="shared" si="21"/>
+        <v>4.3E-3</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <f t="shared" si="17"/>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <f t="shared" si="19"/>
+        <v>1.4190000000000001E-2</v>
+      </c>
+      <c r="N159">
         <f t="shared" si="20"/>
-        <v>4.3E-3</v>
-      </c>
-      <c r="J159">
-        <v>0</v>
-      </c>
-      <c r="K159">
-        <f t="shared" si="16"/>
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="M159">
-        <f t="shared" si="18"/>
-        <v>1.4190000000000001E-2</v>
-      </c>
-      <c r="N159">
-        <f t="shared" si="19"/>
         <v>-1.4190000000000001E-2</v>
       </c>
       <c r="O159">
@@ -18916,25 +18902,25 @@
         <v>47</v>
       </c>
       <c r="I160" s="29">
+        <f t="shared" si="21"/>
+        <v>6.6000000000000008E-3</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <f t="shared" si="17"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <f t="shared" si="19"/>
+        <v>2.1780000000000001E-2</v>
+      </c>
+      <c r="N160">
         <f t="shared" si="20"/>
-        <v>6.6000000000000008E-3</v>
-      </c>
-      <c r="J160">
-        <v>0</v>
-      </c>
-      <c r="K160">
-        <f t="shared" si="16"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160">
-        <f t="shared" si="18"/>
-        <v>2.1780000000000001E-2</v>
-      </c>
-      <c r="N160">
-        <f t="shared" si="19"/>
         <v>-2.1780000000000001E-2</v>
       </c>
       <c r="O160">
@@ -18964,25 +18950,25 @@
         <v>48</v>
       </c>
       <c r="I161" s="29">
+        <f t="shared" si="21"/>
+        <v>3.2500000000000003E-3</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <f t="shared" si="17"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <f t="shared" si="19"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N161">
         <f t="shared" si="20"/>
-        <v>3.2500000000000003E-3</v>
-      </c>
-      <c r="J161">
-        <v>0</v>
-      </c>
-      <c r="K161">
-        <f t="shared" si="16"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161">
-        <f t="shared" si="18"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N161">
-        <f t="shared" si="19"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O161">
@@ -19012,25 +18998,25 @@
         <v>27</v>
       </c>
       <c r="I162" s="29">
+        <f t="shared" si="21"/>
+        <v>5.8000000000000005E-3</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="17"/>
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="19"/>
+        <v>1.9140000000000001E-2</v>
+      </c>
+      <c r="N162">
         <f t="shared" si="20"/>
-        <v>5.8000000000000005E-3</v>
-      </c>
-      <c r="J162">
-        <v>0</v>
-      </c>
-      <c r="K162">
-        <f t="shared" si="16"/>
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162">
-        <f t="shared" si="18"/>
-        <v>1.9140000000000001E-2</v>
-      </c>
-      <c r="N162">
-        <f t="shared" si="19"/>
         <v>-1.9140000000000001E-2</v>
       </c>
       <c r="O162">
@@ -19060,25 +19046,25 @@
         <v>9</v>
       </c>
       <c r="I163" s="29">
+        <f t="shared" si="21"/>
+        <v>3.15E-3</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="17"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="19"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N163">
         <f t="shared" si="20"/>
-        <v>3.15E-3</v>
-      </c>
-      <c r="J163">
-        <v>0</v>
-      </c>
-      <c r="K163">
-        <f t="shared" si="16"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="M163">
-        <f t="shared" si="18"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N163">
-        <f t="shared" si="19"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O163" s="5">
@@ -19114,25 +19100,25 @@
         <v>48</v>
       </c>
       <c r="I164" s="29">
+        <f t="shared" si="21"/>
+        <v>2.9000000000000002E-3</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <f t="shared" si="17"/>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="19"/>
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N164">
         <f t="shared" si="20"/>
-        <v>2.9000000000000002E-3</v>
-      </c>
-      <c r="J164">
-        <v>0</v>
-      </c>
-      <c r="K164">
-        <f t="shared" si="16"/>
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164">
-        <f t="shared" si="18"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N164">
-        <f t="shared" si="19"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O164">
@@ -19162,25 +19148,25 @@
         <v>20</v>
       </c>
       <c r="I165" s="29">
+        <f t="shared" si="21"/>
+        <v>5.7500000000000008E-3</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <f t="shared" si="17"/>
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <f t="shared" si="19"/>
+        <v>1.8975000000000002E-2</v>
+      </c>
+      <c r="N165">
         <f t="shared" si="20"/>
-        <v>5.7500000000000008E-3</v>
-      </c>
-      <c r="J165">
-        <v>0</v>
-      </c>
-      <c r="K165">
-        <f t="shared" si="16"/>
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="M165">
-        <f t="shared" si="18"/>
-        <v>1.8975000000000002E-2</v>
-      </c>
-      <c r="N165">
-        <f t="shared" si="19"/>
         <v>-1.8975000000000002E-2</v>
       </c>
       <c r="O165">
@@ -19210,25 +19196,25 @@
         <v>5</v>
       </c>
       <c r="I166" s="29">
+        <f t="shared" si="21"/>
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <f t="shared" si="17"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <f t="shared" si="19"/>
+        <v>1.7819999999999999E-2</v>
+      </c>
+      <c r="N166">
         <f t="shared" si="20"/>
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="J166">
-        <v>0</v>
-      </c>
-      <c r="K166">
-        <f t="shared" si="16"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166">
-        <f t="shared" si="18"/>
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="N166">
-        <f t="shared" si="19"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O166" s="5">
@@ -19264,25 +19250,25 @@
         <v>3</v>
       </c>
       <c r="I167" s="29">
+        <f t="shared" si="21"/>
+        <v>2.65E-3</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <f t="shared" si="17"/>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <f t="shared" si="19"/>
+        <v>8.745000000000001E-3</v>
+      </c>
+      <c r="N167">
         <f t="shared" si="20"/>
-        <v>2.65E-3</v>
-      </c>
-      <c r="J167">
-        <v>0</v>
-      </c>
-      <c r="K167">
-        <f t="shared" si="16"/>
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167">
-        <f t="shared" si="18"/>
-        <v>8.745000000000001E-3</v>
-      </c>
-      <c r="N167">
-        <f t="shared" si="19"/>
         <v>-8.745000000000001E-3</v>
       </c>
       <c r="O167" s="5">
@@ -19318,25 +19304,25 @@
         <v>19</v>
       </c>
       <c r="I168" s="29">
+        <f t="shared" si="21"/>
+        <v>2.9000000000000002E-3</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <f t="shared" si="17"/>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <f t="shared" si="19"/>
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N168">
         <f t="shared" si="20"/>
-        <v>2.9000000000000002E-3</v>
-      </c>
-      <c r="J168">
-        <v>0</v>
-      </c>
-      <c r="K168">
-        <f t="shared" si="16"/>
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="M168">
-        <f t="shared" si="18"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N168">
-        <f t="shared" si="19"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O168">
@@ -19366,25 +19352,25 @@
         <v>31</v>
       </c>
       <c r="I169" s="29">
+        <f t="shared" si="21"/>
+        <v>3.1000000000000003E-3</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <f t="shared" si="17"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <f t="shared" si="19"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N169">
         <f t="shared" si="20"/>
-        <v>3.1000000000000003E-3</v>
-      </c>
-      <c r="J169">
-        <v>0</v>
-      </c>
-      <c r="K169">
-        <f t="shared" si="16"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="M169">
-        <f t="shared" si="18"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N169">
-        <f t="shared" si="19"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O169">
@@ -19414,25 +19400,25 @@
         <v>31</v>
       </c>
       <c r="I170" s="29">
+        <f t="shared" si="21"/>
+        <v>6.8000000000000005E-3</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <f t="shared" si="17"/>
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <f t="shared" si="19"/>
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="N170">
         <f t="shared" si="20"/>
-        <v>6.8000000000000005E-3</v>
-      </c>
-      <c r="J170">
-        <v>0</v>
-      </c>
-      <c r="K170">
-        <f t="shared" si="16"/>
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="M170">
-        <f t="shared" si="18"/>
-        <v>2.2440000000000002E-2</v>
-      </c>
-      <c r="N170">
-        <f t="shared" si="19"/>
         <v>-2.2440000000000002E-2</v>
       </c>
       <c r="O170">
@@ -19463,25 +19449,25 @@
       </c>
       <c r="H171" s="10"/>
       <c r="I171" s="29">
+        <f t="shared" si="21"/>
+        <v>2.9499999999999999E-3</v>
+      </c>
+      <c r="J171" s="10">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <f t="shared" si="17"/>
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="L171" s="10">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <f t="shared" si="19"/>
+        <v>9.7350000000000006E-3</v>
+      </c>
+      <c r="N171">
         <f t="shared" si="20"/>
-        <v>2.9499999999999999E-3</v>
-      </c>
-      <c r="J171" s="10">
-        <v>0</v>
-      </c>
-      <c r="K171">
-        <f t="shared" si="16"/>
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="L171" s="10">
-        <v>0</v>
-      </c>
-      <c r="M171">
-        <f t="shared" si="18"/>
-        <v>9.7350000000000006E-3</v>
-      </c>
-      <c r="N171">
-        <f t="shared" si="19"/>
         <v>-9.7350000000000006E-3</v>
       </c>
       <c r="O171" s="5">
@@ -19584,7 +19570,7 @@
         <v>272</v>
       </c>
       <c r="E2">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -19593,18 +19579,18 @@
         <v>40</v>
       </c>
       <c r="I2" s="32">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <f>E2/2000</f>
-        <v>1.17</v>
+        <f>1.972/2</f>
+        <v>0.98599999999999999</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-1.17</v>
+        <v>-0.98599999999999999</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -27997,7 +27983,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="J2">
         <v>380</v>
@@ -28041,7 +28027,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="J3">
         <v>380</v>
@@ -28085,7 +28071,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="J4">
         <v>380</v>
@@ -28129,7 +28115,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="J5">
         <v>380</v>
@@ -28173,7 +28159,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="J6">
         <v>380</v>
@@ -28217,7 +28203,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="J7">
         <v>380</v>
@@ -28261,7 +28247,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>10800</v>
+        <v>1000</v>
       </c>
       <c r="J8">
         <v>380</v>
@@ -28305,7 +28291,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="J9">
         <v>380</v>
@@ -28351,7 +28337,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10">
-        <v>11100</v>
+        <v>700</v>
       </c>
       <c r="J10" s="10">
         <v>380</v>
@@ -31598,8 +31584,8 @@
       </c>
       <c r="G83" s="24"/>
       <c r="H83" s="24"/>
-      <c r="I83">
-        <v>2340</v>
+      <c r="I83" s="24">
+        <v>1972</v>
       </c>
       <c r="J83" s="24">
         <v>380</v>

--- a/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
+++ b/TDS_simulation_code/ANDES_Dutch_2035_mpc_cen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2002FC36-5E3A-4883-8D8A-124FFE4A23A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C0A181-0E87-431E-A613-CC3AE8D1B379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28020" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -7837,7 +7837,7 @@
         <v>90</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL2">
         <v>1</v>
@@ -7925,7 +7925,7 @@
         <v>90</v>
       </c>
       <c r="AK3">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL3">
         <v>1</v>
@@ -8013,7 +8013,7 @@
         <v>90</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL4">
         <v>1</v>
@@ -8101,7 +8101,7 @@
         <v>90</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL5">
         <v>1</v>
@@ -8189,7 +8189,7 @@
         <v>90</v>
       </c>
       <c r="AK6">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL6">
         <v>1</v>
@@ -8277,7 +8277,7 @@
         <v>90</v>
       </c>
       <c r="AK7">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL7">
         <v>1</v>
@@ -8365,7 +8365,7 @@
         <v>90</v>
       </c>
       <c r="AK8">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL8">
         <v>1</v>
@@ -8453,7 +8453,7 @@
         <v>90</v>
       </c>
       <c r="AK9">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL9">
         <v>1</v>
